--- a/data_samples/workout_entry_template.xlsx
+++ b/data_samples/workout_entry_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amlim/Downloads/azure-fit-platform/data_samples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{037D8DAF-74D9-0C4F-915D-76FA562E16EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C1D372-813F-284D-9945-75877C6A5A73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41740" yWindow="3260" windowWidth="25460" windowHeight="18340" activeTab="1" xr2:uid="{5828482D-6AAB-A34A-A077-81D95F329610}"/>
+    <workbookView xWindow="28940" yWindow="620" windowWidth="25460" windowHeight="18340" xr2:uid="{5828482D-6AAB-A34A-A077-81D95F329610}"/>
   </bookViews>
   <sheets>
     <sheet name="workout_entry_template" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1321" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1372" uniqueCount="201">
   <si>
     <t>date</t>
   </si>
@@ -225,9 +225,6 @@
     <t>Archer Pullups</t>
   </si>
   <si>
-    <t>Straight Arm Shoulder Raises</t>
-  </si>
-  <si>
     <t>Airwalk pull ups</t>
   </si>
   <si>
@@ -270,9 +267,6 @@
     <t>RB Full Aparts</t>
   </si>
   <si>
-    <t>Straight Arm Raises</t>
-  </si>
-  <si>
     <t>DB Shoulder Shrugs</t>
   </si>
   <si>
@@ -519,27 +513,18 @@
     <t>Air Walk Pullups</t>
   </si>
   <si>
-    <t>Back Lever Heels to Heaven</t>
-  </si>
-  <si>
     <t>Crow Pose</t>
   </si>
   <si>
     <t>Handstand Pushups</t>
   </si>
   <si>
-    <t>Back Lever Tuck Holds</t>
-  </si>
-  <si>
     <t>SL DB Calf Ralses</t>
   </si>
   <si>
     <t>Australian Scapular Pullups</t>
   </si>
   <si>
-    <t>Pseudo Back Lever Tuck Holds</t>
-  </si>
-  <si>
     <t>Reverse Lunges</t>
   </si>
   <si>
@@ -616,6 +601,30 @@
   </si>
   <si>
     <t>Tuck Back Lever</t>
+  </si>
+  <si>
+    <t>Seated Wall Angels (ER)</t>
+  </si>
+  <si>
+    <t>Seated Wall Slides</t>
+  </si>
+  <si>
+    <t>Arm Circles</t>
+  </si>
+  <si>
+    <t>Pseudo Planche SL Knee Tuck Hold</t>
+  </si>
+  <si>
+    <t>DB Lateral Raise Hold</t>
+  </si>
+  <si>
+    <t>Lying DB Pullovers</t>
+  </si>
+  <si>
+    <t>Front Lever Heels to Heaven</t>
+  </si>
+  <si>
+    <t>Front Lever Tuck Holds</t>
   </si>
 </sst>
 </file>
@@ -1477,7 +1486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09805D65-2793-1C46-AB3E-4E9435A12762}">
-  <dimension ref="A1:H426"/>
+  <dimension ref="A1:H443"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.6640625" customWidth="1"/>
@@ -1497,7 +1506,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
@@ -1520,10 +1529,10 @@
         <v>45888</v>
       </c>
       <c r="B2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D2">
         <v>4</v>
@@ -1543,10 +1552,10 @@
         <v>45888</v>
       </c>
       <c r="B3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D3">
         <v>3</v>
@@ -1566,10 +1575,10 @@
         <v>45888</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -1589,10 +1598,10 @@
         <v>45888</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -1612,10 +1621,10 @@
         <v>45888</v>
       </c>
       <c r="B6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -1627,7 +1636,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -1638,7 +1647,7 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -1650,7 +1659,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -1658,10 +1667,10 @@
         <v>45888</v>
       </c>
       <c r="B8" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -1676,7 +1685,7 @@
         <v>7</v>
       </c>
       <c r="H8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -1687,7 +1696,7 @@
         <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -1707,10 +1716,10 @@
         <v>45890</v>
       </c>
       <c r="B10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C10" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D10">
         <v>2</v>
@@ -1730,10 +1739,10 @@
         <v>45890</v>
       </c>
       <c r="B11" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -1756,7 +1765,7 @@
         <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D12">
         <v>2</v>
@@ -1776,10 +1785,10 @@
         <v>45890</v>
       </c>
       <c r="B13" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -1799,10 +1808,10 @@
         <v>45890</v>
       </c>
       <c r="B14" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C14" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D14">
         <v>3</v>
@@ -1825,7 +1834,7 @@
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D15">
         <v>3</v>
@@ -1848,7 +1857,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -1868,10 +1877,10 @@
         <v>45894</v>
       </c>
       <c r="B17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C17" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D17">
         <v>4</v>
@@ -1894,7 +1903,7 @@
         <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D18">
         <v>4</v>
@@ -1906,7 +1915,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1914,10 +1923,10 @@
         <v>45895</v>
       </c>
       <c r="B19" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C19" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -1937,10 +1946,10 @@
         <v>45895</v>
       </c>
       <c r="B20" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C20" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -1963,7 +1972,7 @@
         <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -1975,7 +1984,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
@@ -1986,7 +1995,7 @@
         <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -2009,7 +2018,7 @@
         <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -2029,10 +2038,10 @@
         <v>45895</v>
       </c>
       <c r="B24" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C24" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -2044,7 +2053,7 @@
         <v>0</v>
       </c>
       <c r="G24" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
@@ -2052,10 +2061,10 @@
         <v>45895</v>
       </c>
       <c r="B25" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C25" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -2075,10 +2084,10 @@
         <v>45895</v>
       </c>
       <c r="B26" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C26" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -2101,7 +2110,7 @@
         <v>18</v>
       </c>
       <c r="C27" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D27">
         <v>4</v>
@@ -2124,7 +2133,7 @@
         <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -2144,10 +2153,10 @@
         <v>45895</v>
       </c>
       <c r="B29" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C29" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -2159,7 +2168,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
@@ -2170,7 +2179,7 @@
         <v>19</v>
       </c>
       <c r="C30" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -2190,10 +2199,10 @@
         <v>45895</v>
       </c>
       <c r="B31" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C31" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -2216,7 +2225,7 @@
         <v>20</v>
       </c>
       <c r="C32" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D32">
         <v>4</v>
@@ -2239,7 +2248,7 @@
         <v>21</v>
       </c>
       <c r="C33" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D33">
         <v>4</v>
@@ -2262,7 +2271,7 @@
         <v>22</v>
       </c>
       <c r="C34" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D34">
         <v>3</v>
@@ -2282,10 +2291,10 @@
         <v>45896</v>
       </c>
       <c r="B35" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C35" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -2305,10 +2314,10 @@
         <v>45896</v>
       </c>
       <c r="B36" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C36" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -2328,10 +2337,10 @@
         <v>45896</v>
       </c>
       <c r="B37" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C37" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -2351,10 +2360,10 @@
         <v>45896</v>
       </c>
       <c r="B38" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C38" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -2374,10 +2383,10 @@
         <v>45897</v>
       </c>
       <c r="B39" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C39" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D39">
         <v>2</v>
@@ -2397,10 +2406,10 @@
         <v>45897</v>
       </c>
       <c r="B40" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C40" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D40">
         <v>2</v>
@@ -2420,10 +2429,10 @@
         <v>45897</v>
       </c>
       <c r="B41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C41" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D41">
         <v>3</v>
@@ -2443,10 +2452,10 @@
         <v>45897</v>
       </c>
       <c r="B42" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C42" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D42">
         <v>2</v>
@@ -2469,7 +2478,7 @@
         <v>24</v>
       </c>
       <c r="C43" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D43">
         <v>2</v>
@@ -2481,7 +2490,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
@@ -2492,7 +2501,7 @@
         <v>23</v>
       </c>
       <c r="C44" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D44">
         <v>3</v>
@@ -2512,10 +2521,10 @@
         <v>45897</v>
       </c>
       <c r="B45" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C45" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -2535,10 +2544,10 @@
         <v>45897</v>
       </c>
       <c r="B46" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C46" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -2558,10 +2567,10 @@
         <v>45897</v>
       </c>
       <c r="B47" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C47" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -2581,10 +2590,10 @@
         <v>45897</v>
       </c>
       <c r="B48" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C48" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -2604,10 +2613,10 @@
         <v>45899</v>
       </c>
       <c r="B49" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C49" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D49">
         <v>3</v>
@@ -2630,7 +2639,7 @@
         <v>24</v>
       </c>
       <c r="C50" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D50">
         <v>2</v>
@@ -2642,7 +2651,7 @@
         <v>0</v>
       </c>
       <c r="G50" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
@@ -2653,7 +2662,7 @@
         <v>25</v>
       </c>
       <c r="C51" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D51">
         <v>3</v>
@@ -2665,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="G51" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
@@ -2676,7 +2685,7 @@
         <v>15</v>
       </c>
       <c r="C52" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D52">
         <v>3</v>
@@ -2688,7 +2697,7 @@
         <v>0</v>
       </c>
       <c r="G52" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
@@ -2696,10 +2705,10 @@
         <v>45899</v>
       </c>
       <c r="B53" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C53" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D53">
         <v>3</v>
@@ -2711,7 +2720,7 @@
         <v>0</v>
       </c>
       <c r="G53" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
@@ -2722,7 +2731,7 @@
         <v>27</v>
       </c>
       <c r="C54" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D54">
         <v>2</v>
@@ -2742,10 +2751,10 @@
         <v>45897</v>
       </c>
       <c r="B55" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C55" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -2765,10 +2774,10 @@
         <v>45897</v>
       </c>
       <c r="B56" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C56" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -2788,10 +2797,10 @@
         <v>45897</v>
       </c>
       <c r="B57" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C57" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -2811,10 +2820,10 @@
         <v>45899</v>
       </c>
       <c r="B58" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C58" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D58">
         <v>3</v>
@@ -2837,7 +2846,7 @@
         <v>45</v>
       </c>
       <c r="C59" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D59">
         <v>2</v>
@@ -2857,10 +2866,10 @@
         <v>45899</v>
       </c>
       <c r="B60" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C60" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -2880,10 +2889,10 @@
         <v>45901</v>
       </c>
       <c r="B61" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C61" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D61">
         <v>2</v>
@@ -2906,7 +2915,7 @@
         <v>27</v>
       </c>
       <c r="C62" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D62">
         <v>2</v>
@@ -2926,10 +2935,10 @@
         <v>45901</v>
       </c>
       <c r="B63" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C63" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -2949,10 +2958,10 @@
         <v>45901</v>
       </c>
       <c r="B64" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C64" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -2972,10 +2981,10 @@
         <v>45901</v>
       </c>
       <c r="B65" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C65" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -2995,10 +3004,10 @@
         <v>45901</v>
       </c>
       <c r="B66" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C66" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D66">
         <v>2</v>
@@ -3021,7 +3030,7 @@
         <v>24</v>
       </c>
       <c r="C67" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D67">
         <v>2</v>
@@ -3033,7 +3042,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
@@ -3044,7 +3053,7 @@
         <v>26</v>
       </c>
       <c r="C68" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D68">
         <v>3</v>
@@ -3056,7 +3065,7 @@
         <v>0</v>
       </c>
       <c r="G68" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
@@ -3067,7 +3076,7 @@
         <v>27</v>
       </c>
       <c r="C69" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D69">
         <v>2</v>
@@ -3090,7 +3099,7 @@
         <v>29</v>
       </c>
       <c r="C70" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D70">
         <v>4</v>
@@ -3113,7 +3122,7 @@
         <v>30</v>
       </c>
       <c r="C71" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D71">
         <v>2</v>
@@ -3136,7 +3145,7 @@
         <v>30</v>
       </c>
       <c r="C72" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D72">
         <v>1</v>
@@ -3159,7 +3168,7 @@
         <v>30</v>
       </c>
       <c r="C73" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D73">
         <v>2</v>
@@ -3179,10 +3188,10 @@
         <v>45902</v>
       </c>
       <c r="B74" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C74" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D74">
         <v>3</v>
@@ -3202,10 +3211,10 @@
         <v>45902</v>
       </c>
       <c r="B75" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C75" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D75">
         <v>3</v>
@@ -3225,10 +3234,10 @@
         <v>45902</v>
       </c>
       <c r="B76" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C76" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D76">
         <v>4</v>
@@ -3248,10 +3257,10 @@
         <v>45902</v>
       </c>
       <c r="B77" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C77" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D77">
         <v>3</v>
@@ -3274,7 +3283,7 @@
         <v>32</v>
       </c>
       <c r="C78" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D78">
         <v>3</v>
@@ -3297,7 +3306,7 @@
         <v>33</v>
       </c>
       <c r="C79" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D79">
         <v>2</v>
@@ -3309,7 +3318,7 @@
         <v>0</v>
       </c>
       <c r="G79" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.2">
@@ -3320,7 +3329,7 @@
         <v>28</v>
       </c>
       <c r="C80" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D80">
         <v>4</v>
@@ -3343,7 +3352,7 @@
         <v>35</v>
       </c>
       <c r="C81" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D81">
         <v>3</v>
@@ -3363,10 +3372,10 @@
         <v>45907</v>
       </c>
       <c r="B82" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C82" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D82">
         <v>3</v>
@@ -3389,7 +3398,7 @@
         <v>30</v>
       </c>
       <c r="C83" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D83">
         <v>2</v>
@@ -3412,7 +3421,7 @@
         <v>37</v>
       </c>
       <c r="C84" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D84">
         <v>3</v>
@@ -3432,10 +3441,10 @@
         <v>45907</v>
       </c>
       <c r="B85" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C85" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D85">
         <v>3</v>
@@ -3455,10 +3464,10 @@
         <v>45907</v>
       </c>
       <c r="B86" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C86" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D86">
         <v>3</v>
@@ -3478,10 +3487,10 @@
         <v>45907</v>
       </c>
       <c r="B87" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C87" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D87">
         <v>3</v>
@@ -3501,10 +3510,10 @@
         <v>45910</v>
       </c>
       <c r="B88" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C88" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D88">
         <v>3</v>
@@ -3524,10 +3533,10 @@
         <v>45910</v>
       </c>
       <c r="B89" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C89" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D89">
         <v>3</v>
@@ -3550,7 +3559,7 @@
         <v>30</v>
       </c>
       <c r="C90" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D90">
         <v>4</v>
@@ -3573,7 +3582,7 @@
         <v>37</v>
       </c>
       <c r="C91" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -3596,7 +3605,7 @@
         <v>37</v>
       </c>
       <c r="C92" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D92">
         <v>2</v>
@@ -3616,10 +3625,10 @@
         <v>45910</v>
       </c>
       <c r="B93" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C93" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D93">
         <v>3</v>
@@ -3639,10 +3648,10 @@
         <v>45910</v>
       </c>
       <c r="B94" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C94" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D94">
         <v>3</v>
@@ -3662,10 +3671,10 @@
         <v>45910</v>
       </c>
       <c r="B95" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C95" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D95">
         <v>4</v>
@@ -3685,10 +3694,10 @@
         <v>45910</v>
       </c>
       <c r="B96" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C96" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -3708,10 +3717,10 @@
         <v>45910</v>
       </c>
       <c r="B97" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C97" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -3731,10 +3740,10 @@
         <v>45910</v>
       </c>
       <c r="B98" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C98" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -3754,10 +3763,10 @@
         <v>45916</v>
       </c>
       <c r="B99" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C99" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D99">
         <v>4</v>
@@ -3777,10 +3786,10 @@
         <v>45916</v>
       </c>
       <c r="B100" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C100" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D100">
         <v>2</v>
@@ -3803,7 +3812,7 @@
         <v>27</v>
       </c>
       <c r="C101" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D101">
         <v>3</v>
@@ -3826,7 +3835,7 @@
         <v>35</v>
       </c>
       <c r="C102" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D102">
         <v>3</v>
@@ -3846,10 +3855,10 @@
         <v>45918</v>
       </c>
       <c r="B103" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C103" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D103">
         <v>3</v>
@@ -3872,7 +3881,7 @@
         <v>30</v>
       </c>
       <c r="C104" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D104">
         <v>3</v>
@@ -3895,7 +3904,7 @@
         <v>38</v>
       </c>
       <c r="C105" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D105">
         <v>1</v>
@@ -3918,7 +3927,7 @@
         <v>38</v>
       </c>
       <c r="C106" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D106">
         <v>2</v>
@@ -3938,10 +3947,10 @@
         <v>45918</v>
       </c>
       <c r="B107" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C107" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D107">
         <v>3</v>
@@ -3961,10 +3970,10 @@
         <v>45918</v>
       </c>
       <c r="B108" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C108" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D108">
         <v>3</v>
@@ -3987,7 +3996,7 @@
         <v>34</v>
       </c>
       <c r="C109" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D109">
         <v>3</v>
@@ -4007,10 +4016,10 @@
         <v>45919</v>
       </c>
       <c r="B110" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C110" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D110">
         <v>2</v>
@@ -4030,10 +4039,10 @@
         <v>45919</v>
       </c>
       <c r="B111" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C111" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D111">
         <v>2</v>
@@ -4053,10 +4062,10 @@
         <v>45919</v>
       </c>
       <c r="B112" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C112" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D112">
         <v>2</v>
@@ -4079,7 +4088,7 @@
         <v>53</v>
       </c>
       <c r="C113" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D113">
         <v>4</v>
@@ -4099,10 +4108,10 @@
         <v>45919</v>
       </c>
       <c r="B114" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C114" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D114">
         <v>2</v>
@@ -4122,10 +4131,10 @@
         <v>45919</v>
       </c>
       <c r="B115" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C115" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D115">
         <v>2</v>
@@ -4145,10 +4154,10 @@
         <v>45925</v>
       </c>
       <c r="B116" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C116" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D116">
         <v>3</v>
@@ -4168,10 +4177,10 @@
         <v>45925</v>
       </c>
       <c r="B117" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C117" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D117">
         <v>3</v>
@@ -4194,7 +4203,7 @@
         <v>36</v>
       </c>
       <c r="C118" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D118">
         <v>4</v>
@@ -4214,10 +4223,10 @@
         <v>45925</v>
       </c>
       <c r="B119" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C119" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D119">
         <v>4</v>
@@ -4240,7 +4249,7 @@
         <v>37</v>
       </c>
       <c r="C120" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D120">
         <v>3</v>
@@ -4263,7 +4272,7 @@
         <v>38</v>
       </c>
       <c r="C121" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D121">
         <v>3</v>
@@ -4286,7 +4295,7 @@
         <v>38</v>
       </c>
       <c r="C122" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D122">
         <v>3</v>
@@ -4309,7 +4318,7 @@
         <v>39</v>
       </c>
       <c r="C123" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D123">
         <v>3</v>
@@ -4329,10 +4338,10 @@
         <v>45925</v>
       </c>
       <c r="B124" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C124" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D124">
         <v>3</v>
@@ -4352,10 +4361,10 @@
         <v>45925</v>
       </c>
       <c r="B125" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C125" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D125">
         <v>1</v>
@@ -4375,10 +4384,10 @@
         <v>45925</v>
       </c>
       <c r="B126" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C126" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D126">
         <v>1</v>
@@ -4398,10 +4407,10 @@
         <v>45925</v>
       </c>
       <c r="B127" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C127" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D127">
         <v>1</v>
@@ -4421,10 +4430,10 @@
         <v>45926</v>
       </c>
       <c r="B128" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C128" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -4444,10 +4453,10 @@
         <v>45926</v>
       </c>
       <c r="B129" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C129" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D129">
         <v>1</v>
@@ -4467,10 +4476,10 @@
         <v>45926</v>
       </c>
       <c r="B130" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C130" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D130">
         <v>1</v>
@@ -4490,10 +4499,10 @@
         <v>45926</v>
       </c>
       <c r="B131" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C131" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D131">
         <v>1</v>
@@ -4516,7 +4525,7 @@
         <v>40</v>
       </c>
       <c r="C132" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D132">
         <v>3</v>
@@ -4536,10 +4545,10 @@
         <v>45926</v>
       </c>
       <c r="B133" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C133" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D133">
         <v>3</v>
@@ -4559,10 +4568,10 @@
         <v>45926</v>
       </c>
       <c r="B134" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C134" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D134">
         <v>3</v>
@@ -4585,7 +4594,7 @@
         <v>41</v>
       </c>
       <c r="C135" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D135">
         <v>3</v>
@@ -4608,7 +4617,7 @@
         <v>42</v>
       </c>
       <c r="C136" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D136">
         <v>4</v>
@@ -4628,10 +4637,10 @@
         <v>45929</v>
       </c>
       <c r="B137" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C137" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D137">
         <v>3</v>
@@ -4651,10 +4660,10 @@
         <v>45929</v>
       </c>
       <c r="B138" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C138" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D138">
         <v>3</v>
@@ -4674,10 +4683,10 @@
         <v>45929</v>
       </c>
       <c r="B139" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C139" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D139">
         <v>3</v>
@@ -4700,7 +4709,7 @@
         <v>65</v>
       </c>
       <c r="C140" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D140">
         <v>2</v>
@@ -4723,7 +4732,7 @@
         <v>65</v>
       </c>
       <c r="C141" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D141">
         <v>2</v>
@@ -4746,7 +4755,7 @@
         <v>65</v>
       </c>
       <c r="C142" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D142">
         <v>2</v>
@@ -4769,7 +4778,7 @@
         <v>37</v>
       </c>
       <c r="C143" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D143">
         <v>3</v>
@@ -4789,10 +4798,10 @@
         <v>45929</v>
       </c>
       <c r="B144" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C144" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D144">
         <v>3</v>
@@ -4812,10 +4821,10 @@
         <v>45929</v>
       </c>
       <c r="B145" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C145" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D145">
         <v>2</v>
@@ -4835,10 +4844,10 @@
         <v>45929</v>
       </c>
       <c r="B146" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C146" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D146">
         <v>2</v>
@@ -4861,7 +4870,7 @@
         <v>41</v>
       </c>
       <c r="C147" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D147">
         <v>3</v>
@@ -4884,7 +4893,7 @@
         <v>53</v>
       </c>
       <c r="C148" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D148">
         <v>3</v>
@@ -4904,10 +4913,10 @@
         <v>45932</v>
       </c>
       <c r="B149" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C149" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D149">
         <v>3</v>
@@ -4930,7 +4939,7 @@
         <v>43</v>
       </c>
       <c r="C150" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D150">
         <v>3</v>
@@ -4942,7 +4951,7 @@
         <v>0</v>
       </c>
       <c r="G150" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.2">
@@ -4953,7 +4962,7 @@
         <v>27</v>
       </c>
       <c r="C151" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D151">
         <v>3</v>
@@ -4973,10 +4982,10 @@
         <v>45932</v>
       </c>
       <c r="B152" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C152" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D152">
         <v>1</v>
@@ -4996,10 +5005,10 @@
         <v>45932</v>
       </c>
       <c r="B153" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C153" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D153">
         <v>1</v>
@@ -5019,10 +5028,10 @@
         <v>45932</v>
       </c>
       <c r="B154" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C154" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D154">
         <v>1</v>
@@ -5045,7 +5054,7 @@
         <v>44</v>
       </c>
       <c r="C155" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D155">
         <v>3</v>
@@ -5065,10 +5074,10 @@
         <v>45932</v>
       </c>
       <c r="B156" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C156" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D156">
         <v>4</v>
@@ -5091,7 +5100,7 @@
         <v>46</v>
       </c>
       <c r="C157" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D157">
         <v>3</v>
@@ -5114,7 +5123,7 @@
         <v>30</v>
       </c>
       <c r="C158" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D158">
         <v>2</v>
@@ -5137,7 +5146,7 @@
         <v>30</v>
       </c>
       <c r="C159" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D159">
         <v>2</v>
@@ -5160,7 +5169,7 @@
         <v>47</v>
       </c>
       <c r="C160" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D160">
         <v>3</v>
@@ -5183,7 +5192,7 @@
         <v>48</v>
       </c>
       <c r="C161" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D161">
         <v>3</v>
@@ -5206,7 +5215,7 @@
         <v>49</v>
       </c>
       <c r="C162" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D162">
         <v>3</v>
@@ -5226,10 +5235,10 @@
         <v>45934</v>
       </c>
       <c r="B163" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C163" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D163">
         <v>3</v>
@@ -5249,10 +5258,10 @@
         <v>45934</v>
       </c>
       <c r="B164" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C164" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D164">
         <v>3</v>
@@ -5264,7 +5273,7 @@
         <v>0</v>
       </c>
       <c r="G164" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.2">
@@ -5275,7 +5284,7 @@
         <v>50</v>
       </c>
       <c r="C165" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D165">
         <v>3</v>
@@ -5298,7 +5307,7 @@
         <v>51</v>
       </c>
       <c r="C166" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D166">
         <v>3</v>
@@ -5321,7 +5330,7 @@
         <v>37</v>
       </c>
       <c r="C167" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D167">
         <v>3</v>
@@ -5344,7 +5353,7 @@
         <v>52</v>
       </c>
       <c r="C168" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D168">
         <v>3</v>
@@ -5367,7 +5376,7 @@
         <v>33</v>
       </c>
       <c r="C169" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D169">
         <v>3</v>
@@ -5387,10 +5396,10 @@
         <v>45936</v>
       </c>
       <c r="B170" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C170" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D170">
         <v>4</v>
@@ -5413,7 +5422,7 @@
         <v>53</v>
       </c>
       <c r="C171" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D171">
         <v>3</v>
@@ -5436,7 +5445,7 @@
         <v>54</v>
       </c>
       <c r="C172" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D172">
         <v>3</v>
@@ -5459,7 +5468,7 @@
         <v>55</v>
       </c>
       <c r="C173" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D173">
         <v>3</v>
@@ -5482,7 +5491,7 @@
         <v>52</v>
       </c>
       <c r="C174" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D174">
         <v>3</v>
@@ -5502,10 +5511,10 @@
         <v>45950</v>
       </c>
       <c r="B175" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C175" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D175">
         <v>3</v>
@@ -5528,7 +5537,7 @@
         <v>28</v>
       </c>
       <c r="C176" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D176">
         <v>3</v>
@@ -5551,7 +5560,7 @@
         <v>56</v>
       </c>
       <c r="C177" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D177">
         <v>2</v>
@@ -5574,7 +5583,7 @@
         <v>56</v>
       </c>
       <c r="C178" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D178">
         <v>2</v>
@@ -5594,10 +5603,10 @@
         <v>45950</v>
       </c>
       <c r="B179" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C179" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D179">
         <v>3</v>
@@ -5620,7 +5629,7 @@
         <v>46</v>
       </c>
       <c r="C180" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D180">
         <v>3</v>
@@ -5640,10 +5649,10 @@
         <v>45950</v>
       </c>
       <c r="B181" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C181" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D181">
         <v>3</v>
@@ -5663,10 +5672,10 @@
         <v>45950</v>
       </c>
       <c r="B182" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C182" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D182">
         <v>3</v>
@@ -5686,10 +5695,10 @@
         <v>45953</v>
       </c>
       <c r="B183" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C183" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D183">
         <v>3</v>
@@ -5712,7 +5721,7 @@
         <v>61</v>
       </c>
       <c r="C184" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D184">
         <v>3</v>
@@ -5732,10 +5741,10 @@
         <v>45953</v>
       </c>
       <c r="B185" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C185" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D185">
         <v>2</v>
@@ -5755,10 +5764,10 @@
         <v>45953</v>
       </c>
       <c r="B186" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C186" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D186">
         <v>2</v>
@@ -5778,10 +5787,10 @@
         <v>45953</v>
       </c>
       <c r="B187" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C187" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D187">
         <v>2</v>
@@ -5801,10 +5810,10 @@
         <v>45953</v>
       </c>
       <c r="B188" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C188" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D188">
         <v>2</v>
@@ -5824,10 +5833,10 @@
         <v>45953</v>
       </c>
       <c r="B189" t="s">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="C189" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D189">
         <v>1</v>
@@ -5847,10 +5856,10 @@
         <v>45953</v>
       </c>
       <c r="B190" t="s">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="C190" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D190">
         <v>1</v>
@@ -5870,10 +5879,10 @@
         <v>45953</v>
       </c>
       <c r="B191" t="s">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="C191" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D191">
         <v>1</v>
@@ -5896,7 +5905,7 @@
         <v>30</v>
       </c>
       <c r="C192" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D192">
         <v>2</v>
@@ -5919,7 +5928,7 @@
         <v>30</v>
       </c>
       <c r="C193" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D193">
         <v>1</v>
@@ -5939,10 +5948,10 @@
         <v>45953</v>
       </c>
       <c r="B194" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C194" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D194">
         <v>3</v>
@@ -5962,10 +5971,10 @@
         <v>45953</v>
       </c>
       <c r="B195" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C195" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D195">
         <v>2</v>
@@ -5985,10 +5994,10 @@
         <v>45953</v>
       </c>
       <c r="B196" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C196" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D196">
         <v>2</v>
@@ -6011,7 +6020,7 @@
         <v>28</v>
       </c>
       <c r="C197" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D197">
         <v>3</v>
@@ -6034,7 +6043,7 @@
         <v>61</v>
       </c>
       <c r="C198" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D198">
         <v>4</v>
@@ -6054,10 +6063,10 @@
         <v>45954</v>
       </c>
       <c r="B199" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C199" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D199">
         <v>3</v>
@@ -6077,10 +6086,10 @@
         <v>45954</v>
       </c>
       <c r="B200" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C200" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D200">
         <v>3</v>
@@ -6100,10 +6109,10 @@
         <v>45954</v>
       </c>
       <c r="B201" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C201" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D201">
         <v>3</v>
@@ -6123,10 +6132,10 @@
         <v>45954</v>
       </c>
       <c r="B202" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C202" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D202">
         <v>3</v>
@@ -6146,10 +6155,10 @@
         <v>45954</v>
       </c>
       <c r="B203" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C203" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D203">
         <v>3</v>
@@ -6172,7 +6181,7 @@
         <v>20</v>
       </c>
       <c r="C204" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D204">
         <v>3</v>
@@ -6192,10 +6201,10 @@
         <v>45958</v>
       </c>
       <c r="B205" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C205" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D205">
         <v>4</v>
@@ -6218,7 +6227,7 @@
         <v>50</v>
       </c>
       <c r="C206" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D206">
         <v>4</v>
@@ -6238,10 +6247,10 @@
         <v>45958</v>
       </c>
       <c r="B207" t="s">
-        <v>168</v>
+        <v>200</v>
       </c>
       <c r="C207" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D207">
         <v>2</v>
@@ -6264,7 +6273,7 @@
         <v>33</v>
       </c>
       <c r="C208" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D208">
         <v>2</v>
@@ -6276,7 +6285,7 @@
         <v>0</v>
       </c>
       <c r="G208" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.2">
@@ -6287,7 +6296,7 @@
         <v>61</v>
       </c>
       <c r="C209" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D209">
         <v>3</v>
@@ -6310,7 +6319,7 @@
         <v>57</v>
       </c>
       <c r="C210" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D210">
         <v>3</v>
@@ -6333,7 +6342,7 @@
         <v>30</v>
       </c>
       <c r="C211" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D211">
         <v>3</v>
@@ -6353,10 +6362,10 @@
         <v>45959</v>
       </c>
       <c r="B212" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C212" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D212">
         <v>3</v>
@@ -6376,10 +6385,10 @@
         <v>45959</v>
       </c>
       <c r="B213" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C213" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D213">
         <v>4</v>
@@ -6399,10 +6408,10 @@
         <v>45959</v>
       </c>
       <c r="B214" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C214" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D214">
         <v>4</v>
@@ -6422,10 +6431,10 @@
         <v>45959</v>
       </c>
       <c r="B215" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C215" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D215">
         <v>3</v>
@@ -6445,10 +6454,10 @@
         <v>45959</v>
       </c>
       <c r="B216" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C216" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D216">
         <v>3</v>
@@ -6471,7 +6480,7 @@
         <v>37</v>
       </c>
       <c r="C217" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D217">
         <v>1</v>
@@ -6494,7 +6503,7 @@
         <v>58</v>
       </c>
       <c r="C218" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D218">
         <v>4</v>
@@ -6517,7 +6526,7 @@
         <v>33</v>
       </c>
       <c r="C219" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D219">
         <v>2</v>
@@ -6540,7 +6549,7 @@
         <v>59</v>
       </c>
       <c r="C220" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D220">
         <v>3</v>
@@ -6560,10 +6569,10 @@
         <v>45962</v>
       </c>
       <c r="B221" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C221" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D221">
         <v>2</v>
@@ -6583,10 +6592,10 @@
         <v>45962</v>
       </c>
       <c r="B222" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C222" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D222">
         <v>2</v>
@@ -6606,10 +6615,10 @@
         <v>45962</v>
       </c>
       <c r="B223" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C223" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D223">
         <v>3</v>
@@ -6632,7 +6641,7 @@
         <v>60</v>
       </c>
       <c r="C224" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D224">
         <v>2</v>
@@ -6652,10 +6661,10 @@
         <v>45962</v>
       </c>
       <c r="B225" t="s">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="C225" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D225">
         <v>3</v>
@@ -6675,10 +6684,10 @@
         <v>45962</v>
       </c>
       <c r="B226" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C226" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D226">
         <v>3</v>
@@ -6701,7 +6710,7 @@
         <v>61</v>
       </c>
       <c r="C227" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D227">
         <v>4</v>
@@ -6724,7 +6733,7 @@
         <v>33</v>
       </c>
       <c r="C228" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D228">
         <v>2</v>
@@ -6736,7 +6745,7 @@
         <v>0</v>
       </c>
       <c r="G228" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.2">
@@ -6747,7 +6756,7 @@
         <v>28</v>
       </c>
       <c r="C229" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D229">
         <v>2</v>
@@ -6770,7 +6779,7 @@
         <v>28</v>
       </c>
       <c r="C230" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D230">
         <v>2</v>
@@ -6793,7 +6802,7 @@
         <v>56</v>
       </c>
       <c r="C231" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D231">
         <v>4</v>
@@ -6816,7 +6825,7 @@
         <v>62</v>
       </c>
       <c r="C232" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D232">
         <v>4</v>
@@ -6836,10 +6845,10 @@
         <v>45966</v>
       </c>
       <c r="B233" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C233" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D233">
         <v>2</v>
@@ -6862,7 +6871,7 @@
         <v>48</v>
       </c>
       <c r="C234" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D234">
         <v>2</v>
@@ -6885,7 +6894,7 @@
         <v>37</v>
       </c>
       <c r="C235" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D235">
         <v>2</v>
@@ -6908,7 +6917,7 @@
         <v>37</v>
       </c>
       <c r="C236" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D236">
         <v>2</v>
@@ -6928,10 +6937,10 @@
         <v>45967</v>
       </c>
       <c r="B237" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C237" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D237">
         <v>3</v>
@@ -6951,10 +6960,10 @@
         <v>45967</v>
       </c>
       <c r="B238" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C238" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D238">
         <v>3</v>
@@ -6974,10 +6983,10 @@
         <v>45967</v>
       </c>
       <c r="B239" t="s">
-        <v>168</v>
+        <v>200</v>
       </c>
       <c r="C239" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D239">
         <v>4</v>
@@ -7000,7 +7009,7 @@
         <v>30</v>
       </c>
       <c r="C240" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D240">
         <v>3</v>
@@ -7020,10 +7029,10 @@
         <v>45967</v>
       </c>
       <c r="B241" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C241" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D241">
         <v>3</v>
@@ -7046,7 +7055,7 @@
         <v>59</v>
       </c>
       <c r="C242" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D242">
         <v>3</v>
@@ -7069,7 +7078,7 @@
         <v>37</v>
       </c>
       <c r="C243" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D243">
         <v>4</v>
@@ -7092,7 +7101,7 @@
         <v>33</v>
       </c>
       <c r="C244" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D244">
         <v>2</v>
@@ -7115,7 +7124,7 @@
         <v>63</v>
       </c>
       <c r="C245" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D245">
         <v>3</v>
@@ -7138,7 +7147,7 @@
         <v>61</v>
       </c>
       <c r="C246" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D246">
         <v>3</v>
@@ -7161,7 +7170,7 @@
         <v>64</v>
       </c>
       <c r="C247" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D247">
         <v>3</v>
@@ -7184,7 +7193,7 @@
         <v>65</v>
       </c>
       <c r="C248" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D248">
         <v>2</v>
@@ -7207,7 +7216,7 @@
         <v>65</v>
       </c>
       <c r="C249" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D249">
         <v>2</v>
@@ -7227,10 +7236,10 @@
         <v>45970</v>
       </c>
       <c r="B250" t="s">
-        <v>67</v>
+        <v>198</v>
       </c>
       <c r="C250" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D250">
         <v>4</v>
@@ -7250,10 +7259,10 @@
         <v>45970</v>
       </c>
       <c r="B251" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C251" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D251">
         <v>3</v>
@@ -7276,7 +7285,7 @@
         <v>44</v>
       </c>
       <c r="C252" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D252">
         <v>2</v>
@@ -7296,10 +7305,10 @@
         <v>45972</v>
       </c>
       <c r="B253" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C253" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D253">
         <v>1</v>
@@ -7319,10 +7328,10 @@
         <v>45972</v>
       </c>
       <c r="B254" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C254" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D254">
         <v>1</v>
@@ -7342,10 +7351,10 @@
         <v>45972</v>
       </c>
       <c r="B255" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C255" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D255">
         <v>1</v>
@@ -7368,7 +7377,7 @@
         <v>66</v>
       </c>
       <c r="C256" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D256">
         <v>3</v>
@@ -7388,10 +7397,10 @@
         <v>45972</v>
       </c>
       <c r="B257" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C257" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D257">
         <v>3</v>
@@ -7414,7 +7423,7 @@
         <v>50</v>
       </c>
       <c r="C258" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D258">
         <v>3</v>
@@ -7434,10 +7443,10 @@
         <v>45972</v>
       </c>
       <c r="B259" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C259" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D259">
         <v>2</v>
@@ -7457,10 +7466,10 @@
         <v>45972</v>
       </c>
       <c r="B260" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C260" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D260">
         <v>2</v>
@@ -7480,10 +7489,10 @@
         <v>45973</v>
       </c>
       <c r="B261" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C261" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D261">
         <v>2</v>
@@ -7506,7 +7515,7 @@
         <v>30</v>
       </c>
       <c r="C262" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D262">
         <v>3</v>
@@ -7529,7 +7538,7 @@
         <v>37</v>
       </c>
       <c r="C263" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D263">
         <v>3</v>
@@ -7552,7 +7561,7 @@
         <v>9</v>
       </c>
       <c r="C264" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D264">
         <v>4</v>
@@ -7572,10 +7581,10 @@
         <v>45973</v>
       </c>
       <c r="B265" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C265" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D265">
         <v>4</v>
@@ -7595,10 +7604,10 @@
         <v>45973</v>
       </c>
       <c r="B266" t="s">
-        <v>67</v>
+        <v>198</v>
       </c>
       <c r="C266" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D266">
         <v>3</v>
@@ -7618,10 +7627,10 @@
         <v>45977</v>
       </c>
       <c r="B267" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C267" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D267">
         <v>3</v>
@@ -7644,7 +7653,7 @@
         <v>30</v>
       </c>
       <c r="C268" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D268">
         <v>3</v>
@@ -7664,10 +7673,10 @@
         <v>45977</v>
       </c>
       <c r="B269" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C269" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D269">
         <v>3</v>
@@ -7690,7 +7699,7 @@
         <v>33</v>
       </c>
       <c r="C270" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D270">
         <v>2</v>
@@ -7710,10 +7719,10 @@
         <v>45977</v>
       </c>
       <c r="B271" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C271" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D271">
         <v>2</v>
@@ -7733,10 +7742,10 @@
         <v>45977</v>
       </c>
       <c r="B272" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C272" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D272">
         <v>2</v>
@@ -7756,10 +7765,10 @@
         <v>45977</v>
       </c>
       <c r="B273" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C273" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D273">
         <v>1</v>
@@ -7779,10 +7788,10 @@
         <v>45977</v>
       </c>
       <c r="B274" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C274" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D274">
         <v>1</v>
@@ -7802,10 +7811,10 @@
         <v>45977</v>
       </c>
       <c r="B275" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C275" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D275">
         <v>4</v>
@@ -7825,10 +7834,10 @@
         <v>45977</v>
       </c>
       <c r="B276" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C276" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D276">
         <v>4</v>
@@ -7848,10 +7857,10 @@
         <v>45977</v>
       </c>
       <c r="B277" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C277" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D277">
         <v>2</v>
@@ -7874,7 +7883,7 @@
         <v>61</v>
       </c>
       <c r="C278" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D278">
         <v>4</v>
@@ -7894,7 +7903,7 @@
         <v>45980</v>
       </c>
       <c r="B279" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F279">
         <v>100</v>
@@ -7911,7 +7920,7 @@
         <v>58</v>
       </c>
       <c r="C280" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D280">
         <v>3</v>
@@ -7934,7 +7943,7 @@
         <v>66</v>
       </c>
       <c r="C281" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D281">
         <v>3</v>
@@ -7957,7 +7966,7 @@
         <v>30</v>
       </c>
       <c r="C282" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D282">
         <v>3</v>
@@ -7977,10 +7986,10 @@
         <v>45980</v>
       </c>
       <c r="B283" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C283" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D283">
         <v>3</v>
@@ -8000,10 +8009,10 @@
         <v>45980</v>
       </c>
       <c r="B284" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C284" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D284">
         <v>2</v>
@@ -8023,10 +8032,10 @@
         <v>45980</v>
       </c>
       <c r="B285" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C285" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D285">
         <v>1</v>
@@ -8046,10 +8055,10 @@
         <v>45980</v>
       </c>
       <c r="B286" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C286" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D286">
         <v>3</v>
@@ -8069,10 +8078,10 @@
         <v>45981</v>
       </c>
       <c r="B287" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C287" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D287">
         <v>4</v>
@@ -8092,10 +8101,10 @@
         <v>45981</v>
       </c>
       <c r="B288" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C288" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D288">
         <v>2</v>
@@ -8118,7 +8127,7 @@
         <v>31</v>
       </c>
       <c r="C289" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D289">
         <v>4</v>
@@ -8141,7 +8150,7 @@
         <v>65</v>
       </c>
       <c r="C290" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D290">
         <v>2</v>
@@ -8164,7 +8173,7 @@
         <v>65</v>
       </c>
       <c r="C291" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D291">
         <v>2</v>
@@ -8187,7 +8196,7 @@
         <v>65</v>
       </c>
       <c r="C292" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D292">
         <v>2</v>
@@ -8210,7 +8219,7 @@
         <v>44</v>
       </c>
       <c r="C293" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D293">
         <v>23</v>
@@ -8230,10 +8239,10 @@
         <v>45986</v>
       </c>
       <c r="B294" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C294" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D294">
         <v>3</v>
@@ -8253,10 +8262,10 @@
         <v>45986</v>
       </c>
       <c r="B295" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C295" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D295">
         <v>1</v>
@@ -8276,10 +8285,10 @@
         <v>45986</v>
       </c>
       <c r="B296" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C296" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D296">
         <v>1</v>
@@ -8299,10 +8308,10 @@
         <v>45986</v>
       </c>
       <c r="B297" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C297" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D297">
         <v>1</v>
@@ -8322,10 +8331,10 @@
         <v>45986</v>
       </c>
       <c r="B298" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C298" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D298">
         <v>3</v>
@@ -8345,10 +8354,10 @@
         <v>45986</v>
       </c>
       <c r="B299" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C299" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D299">
         <v>3</v>
@@ -8368,10 +8377,10 @@
         <v>45986</v>
       </c>
       <c r="B300" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C300" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D300">
         <v>3</v>
@@ -8391,10 +8400,10 @@
         <v>45986</v>
       </c>
       <c r="B301" t="s">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="C301" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D301">
         <v>3</v>
@@ -8417,7 +8426,7 @@
         <v>30</v>
       </c>
       <c r="C302" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D302">
         <v>1</v>
@@ -8440,7 +8449,7 @@
         <v>30</v>
       </c>
       <c r="C303" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D303">
         <v>2</v>
@@ -8460,10 +8469,10 @@
         <v>45988</v>
       </c>
       <c r="B304" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C304" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D304">
         <v>3</v>
@@ -8483,10 +8492,10 @@
         <v>45988</v>
       </c>
       <c r="B305" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C305" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D305">
         <v>3</v>
@@ -8498,7 +8507,7 @@
         <v>0</v>
       </c>
       <c r="G305" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.2">
@@ -8506,10 +8515,10 @@
         <v>45988</v>
       </c>
       <c r="B306" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C306" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D306">
         <v>3</v>
@@ -8529,10 +8538,10 @@
         <v>45988</v>
       </c>
       <c r="B307" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C307" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D307">
         <v>3</v>
@@ -8552,10 +8561,10 @@
         <v>45988</v>
       </c>
       <c r="B308" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C308" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D308">
         <v>2</v>
@@ -8575,10 +8584,10 @@
         <v>45988</v>
       </c>
       <c r="B309" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C309" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D309">
         <v>3</v>
@@ -8598,10 +8607,10 @@
         <v>45990</v>
       </c>
       <c r="B310" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C310" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D310">
         <v>3</v>
@@ -8621,10 +8630,10 @@
         <v>45990</v>
       </c>
       <c r="B311" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C311" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D311">
         <v>3</v>
@@ -8647,7 +8656,7 @@
         <v>30</v>
       </c>
       <c r="C312" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D312">
         <v>1</v>
@@ -8670,7 +8679,7 @@
         <v>30</v>
       </c>
       <c r="C313" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D313">
         <v>1</v>
@@ -8693,7 +8702,7 @@
         <v>30</v>
       </c>
       <c r="C314" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D314">
         <v>2</v>
@@ -8713,10 +8722,10 @@
         <v>45990</v>
       </c>
       <c r="B315" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C315" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D315">
         <v>3</v>
@@ -8736,10 +8745,10 @@
         <v>45990</v>
       </c>
       <c r="B316" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C316" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D316">
         <v>2</v>
@@ -8759,10 +8768,10 @@
         <v>45990</v>
       </c>
       <c r="B317" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C317" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D317">
         <v>3</v>
@@ -8785,7 +8794,7 @@
         <v>50</v>
       </c>
       <c r="C318" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D318">
         <v>3</v>
@@ -8805,10 +8814,10 @@
         <v>45990</v>
       </c>
       <c r="B319" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C319" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D319">
         <v>3</v>
@@ -8828,10 +8837,10 @@
         <v>45990</v>
       </c>
       <c r="B320" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C320" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D320">
         <v>1</v>
@@ -8851,10 +8860,10 @@
         <v>45990</v>
       </c>
       <c r="B321" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C321" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D321">
         <v>1</v>
@@ -8874,10 +8883,10 @@
         <v>45990</v>
       </c>
       <c r="B322" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C322" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D322">
         <v>1</v>
@@ -8897,10 +8906,10 @@
         <v>45990</v>
       </c>
       <c r="B323" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C323" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D323">
         <v>3</v>
@@ -8920,10 +8929,10 @@
         <v>45991</v>
       </c>
       <c r="B324" t="s">
-        <v>67</v>
+        <v>198</v>
       </c>
       <c r="C324" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D324">
         <v>2</v>
@@ -8946,7 +8955,7 @@
         <v>33</v>
       </c>
       <c r="C325" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D325">
         <v>2</v>
@@ -8966,10 +8975,10 @@
         <v>45991</v>
       </c>
       <c r="B326" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C326" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D326">
         <v>2</v>
@@ -8989,10 +8998,10 @@
         <v>45991</v>
       </c>
       <c r="B327" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C327" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D327">
         <v>2</v>
@@ -9012,10 +9021,10 @@
         <v>45991</v>
       </c>
       <c r="B328" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C328" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D328">
         <v>3</v>
@@ -9035,10 +9044,10 @@
         <v>45991</v>
       </c>
       <c r="B329" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C329" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D329">
         <v>3</v>
@@ -9058,10 +9067,10 @@
         <v>45991</v>
       </c>
       <c r="B330" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C330" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D330">
         <v>4</v>
@@ -9084,7 +9093,7 @@
         <v>64</v>
       </c>
       <c r="C331" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D331">
         <v>2</v>
@@ -9104,10 +9113,10 @@
         <v>45993</v>
       </c>
       <c r="B332" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C332" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D332">
         <v>2</v>
@@ -9119,7 +9128,7 @@
         <v>0</v>
       </c>
       <c r="G332" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.2">
@@ -9130,7 +9139,7 @@
         <v>59</v>
       </c>
       <c r="C333" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D333">
         <v>3</v>
@@ -9150,10 +9159,10 @@
         <v>45993</v>
       </c>
       <c r="B334" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C334" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D334">
         <v>3</v>
@@ -9173,10 +9182,10 @@
         <v>45993</v>
       </c>
       <c r="B335" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C335" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D335">
         <v>3</v>
@@ -9196,10 +9205,10 @@
         <v>45993</v>
       </c>
       <c r="B336" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C336" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D336">
         <v>1</v>
@@ -9219,10 +9228,10 @@
         <v>45993</v>
       </c>
       <c r="B337" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C337" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D337">
         <v>2</v>
@@ -9234,7 +9243,7 @@
         <v>0</v>
       </c>
       <c r="G337" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.2">
@@ -9242,10 +9251,10 @@
         <v>45993</v>
       </c>
       <c r="B338" t="s">
-        <v>67</v>
+        <v>198</v>
       </c>
       <c r="C338" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D338">
         <v>4</v>
@@ -9265,10 +9274,10 @@
         <v>45993</v>
       </c>
       <c r="B339" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C339" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D339">
         <v>4</v>
@@ -9288,10 +9297,10 @@
         <v>45994</v>
       </c>
       <c r="B340" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C340" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D340">
         <v>4</v>
@@ -9314,7 +9323,7 @@
         <v>30</v>
       </c>
       <c r="C341" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D341">
         <v>1</v>
@@ -9337,7 +9346,7 @@
         <v>30</v>
       </c>
       <c r="C342" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D342">
         <v>1</v>
@@ -9357,10 +9366,10 @@
         <v>45994</v>
       </c>
       <c r="B343" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C343" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D343">
         <v>2</v>
@@ -9380,10 +9389,10 @@
         <v>45994</v>
       </c>
       <c r="B344" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C344" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D344">
         <v>2</v>
@@ -9403,10 +9412,10 @@
         <v>45994</v>
       </c>
       <c r="B345" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C345" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D345">
         <v>2</v>
@@ -9426,10 +9435,10 @@
         <v>45994</v>
       </c>
       <c r="B346" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C346" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D346">
         <v>2</v>
@@ -9449,10 +9458,10 @@
         <v>45994</v>
       </c>
       <c r="B347" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C347" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D347">
         <v>2</v>
@@ -9475,7 +9484,7 @@
         <v>37</v>
       </c>
       <c r="C348" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D348">
         <v>3</v>
@@ -9495,10 +9504,10 @@
         <v>45994</v>
       </c>
       <c r="B349" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C349" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D349">
         <v>4</v>
@@ -9518,10 +9527,10 @@
         <v>45995</v>
       </c>
       <c r="B350" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C350" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D350">
         <v>3</v>
@@ -9544,7 +9553,7 @@
         <v>64</v>
       </c>
       <c r="C351" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D351">
         <v>2</v>
@@ -9564,10 +9573,10 @@
         <v>45995</v>
       </c>
       <c r="B352" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C352" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D352">
         <v>2</v>
@@ -9590,7 +9599,7 @@
         <v>20</v>
       </c>
       <c r="C353" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D353">
         <v>2</v>
@@ -9613,7 +9622,7 @@
         <v>20</v>
       </c>
       <c r="C354" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D354">
         <v>2</v>
@@ -9633,10 +9642,10 @@
         <v>45995</v>
       </c>
       <c r="B355" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C355" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D355">
         <v>3</v>
@@ -9656,10 +9665,10 @@
         <v>45995</v>
       </c>
       <c r="B356" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C356" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D356">
         <v>2</v>
@@ -9682,7 +9691,7 @@
         <v>33</v>
       </c>
       <c r="C357" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D357">
         <v>2</v>
@@ -9705,7 +9714,7 @@
         <v>61</v>
       </c>
       <c r="C358" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D358">
         <v>2</v>
@@ -9725,10 +9734,10 @@
         <v>45995</v>
       </c>
       <c r="B359" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C359" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D359">
         <v>3</v>
@@ -9751,7 +9760,7 @@
         <v>33</v>
       </c>
       <c r="C360" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D360">
         <v>3</v>
@@ -9763,7 +9772,7 @@
         <v>0</v>
       </c>
       <c r="G360" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.2">
@@ -9771,10 +9780,10 @@
         <v>45998</v>
       </c>
       <c r="B361" t="s">
-        <v>67</v>
+        <v>198</v>
       </c>
       <c r="C361" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D361">
         <v>3</v>
@@ -9794,10 +9803,10 @@
         <v>45998</v>
       </c>
       <c r="B362" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C362" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D362">
         <v>3</v>
@@ -9820,7 +9829,7 @@
         <v>56</v>
       </c>
       <c r="C363" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D363">
         <v>2</v>
@@ -9840,10 +9849,10 @@
         <v>45998</v>
       </c>
       <c r="B364" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C364" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D364">
         <v>3</v>
@@ -9855,7 +9864,7 @@
         <v>0</v>
       </c>
       <c r="G364" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.2">
@@ -9866,7 +9875,7 @@
         <v>53</v>
       </c>
       <c r="C365" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D365">
         <v>3</v>
@@ -9889,7 +9898,7 @@
         <v>9</v>
       </c>
       <c r="C366" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D366">
         <v>4</v>
@@ -9909,10 +9918,10 @@
         <v>45999</v>
       </c>
       <c r="B367" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C367" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D367">
         <v>3</v>
@@ -9932,10 +9941,10 @@
         <v>45999</v>
       </c>
       <c r="B368" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C368" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D368">
         <v>3</v>
@@ -9955,10 +9964,10 @@
         <v>45999</v>
       </c>
       <c r="B369" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C369" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D369">
         <v>3</v>
@@ -9978,10 +9987,10 @@
         <v>45999</v>
       </c>
       <c r="B370" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C370" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D370">
         <v>4</v>
@@ -10001,10 +10010,10 @@
         <v>45999</v>
       </c>
       <c r="B371" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C371" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D371">
         <v>3</v>
@@ -10024,10 +10033,10 @@
         <v>45999</v>
       </c>
       <c r="B372" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C372" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D372">
         <v>3</v>
@@ -10039,7 +10048,7 @@
         <v>0</v>
       </c>
       <c r="G372" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.2">
@@ -10047,10 +10056,10 @@
         <v>46000</v>
       </c>
       <c r="B373" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C373" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D373">
         <v>3</v>
@@ -10073,7 +10082,7 @@
         <v>59</v>
       </c>
       <c r="C374" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D374">
         <v>3</v>
@@ -10096,7 +10105,7 @@
         <v>52</v>
       </c>
       <c r="C375" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D375">
         <v>3</v>
@@ -10119,7 +10128,7 @@
         <v>33</v>
       </c>
       <c r="C376" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D376">
         <v>2</v>
@@ -10139,10 +10148,10 @@
         <v>46000</v>
       </c>
       <c r="B377" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C377" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D377">
         <v>3</v>
@@ -10162,10 +10171,10 @@
         <v>46000</v>
       </c>
       <c r="B378" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C378" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D378">
         <v>3</v>
@@ -10185,10 +10194,10 @@
         <v>46000</v>
       </c>
       <c r="B379" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C379" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D379">
         <v>3</v>
@@ -10208,10 +10217,10 @@
         <v>46000</v>
       </c>
       <c r="B380" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C380" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D380">
         <v>2</v>
@@ -10234,7 +10243,7 @@
         <v>30</v>
       </c>
       <c r="C381" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D381">
         <v>2</v>
@@ -10257,7 +10266,7 @@
         <v>30</v>
       </c>
       <c r="C382" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D382">
         <v>2</v>
@@ -10280,7 +10289,7 @@
         <v>30</v>
       </c>
       <c r="C383" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D383">
         <v>2</v>
@@ -10300,10 +10309,10 @@
         <v>46001</v>
       </c>
       <c r="B384" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C384" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D384">
         <v>3</v>
@@ -10323,10 +10332,10 @@
         <v>46001</v>
       </c>
       <c r="B385" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C385" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D385">
         <v>3</v>
@@ -10346,10 +10355,10 @@
         <v>46001</v>
       </c>
       <c r="B386" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C386" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D386">
         <v>2</v>
@@ -10369,10 +10378,10 @@
         <v>46001</v>
       </c>
       <c r="B387" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C387" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D387">
         <v>2</v>
@@ -10392,10 +10401,10 @@
         <v>46002</v>
       </c>
       <c r="B388" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C388" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D388">
         <v>3</v>
@@ -10418,7 +10427,7 @@
         <v>33</v>
       </c>
       <c r="C389" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D389">
         <v>2</v>
@@ -10441,7 +10450,7 @@
         <v>53</v>
       </c>
       <c r="C390" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D390">
         <v>3</v>
@@ -10464,7 +10473,7 @@
         <v>9</v>
       </c>
       <c r="C391" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D391">
         <v>4</v>
@@ -10484,10 +10493,10 @@
         <v>46002</v>
       </c>
       <c r="B392" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C392" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D392">
         <v>4</v>
@@ -10510,7 +10519,7 @@
         <v>33</v>
       </c>
       <c r="C393" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D393">
         <v>2</v>
@@ -10530,10 +10539,10 @@
         <v>46005</v>
       </c>
       <c r="B394" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C394" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D394">
         <v>3</v>
@@ -10553,10 +10562,10 @@
         <v>46005</v>
       </c>
       <c r="B395" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C395" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D395">
         <v>3</v>
@@ -10576,10 +10585,10 @@
         <v>46005</v>
       </c>
       <c r="B396" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C396" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D396">
         <v>3</v>
@@ -10599,10 +10608,10 @@
         <v>46005</v>
       </c>
       <c r="B397" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C397" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D397">
         <v>4</v>
@@ -10622,10 +10631,10 @@
         <v>46005</v>
       </c>
       <c r="B398" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C398" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D398">
         <v>3</v>
@@ -10648,7 +10657,7 @@
         <v>30</v>
       </c>
       <c r="C399" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D399">
         <v>3</v>
@@ -10668,10 +10677,10 @@
         <v>46005</v>
       </c>
       <c r="B400" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C400" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D400">
         <v>3</v>
@@ -10691,10 +10700,10 @@
         <v>46005</v>
       </c>
       <c r="B401" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C401" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D401">
         <v>3</v>
@@ -10717,7 +10726,7 @@
         <v>37</v>
       </c>
       <c r="C402" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D402">
         <v>3</v>
@@ -10737,10 +10746,10 @@
         <v>46005</v>
       </c>
       <c r="B403" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C403" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D403">
         <v>3</v>
@@ -10760,10 +10769,10 @@
         <v>46007</v>
       </c>
       <c r="B404" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C404" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D404">
         <v>3</v>
@@ -10786,7 +10795,7 @@
         <v>59</v>
       </c>
       <c r="C405" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D405">
         <v>2</v>
@@ -10806,10 +10815,10 @@
         <v>46007</v>
       </c>
       <c r="B406" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C406" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D406">
         <v>2</v>
@@ -10829,10 +10838,10 @@
         <v>46007</v>
       </c>
       <c r="B407" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C407" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D407">
         <v>4</v>
@@ -10852,10 +10861,10 @@
         <v>46007</v>
       </c>
       <c r="B408" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C408" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D408">
         <v>2</v>
@@ -10875,10 +10884,10 @@
         <v>46007</v>
       </c>
       <c r="B409" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C409" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D409">
         <v>4</v>
@@ -10898,10 +10907,10 @@
         <v>46007</v>
       </c>
       <c r="B410" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C410" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D410">
         <v>3</v>
@@ -10921,10 +10930,10 @@
         <v>46007</v>
       </c>
       <c r="B411" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C411" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D411">
         <v>3</v>
@@ -10944,10 +10953,10 @@
         <v>46008</v>
       </c>
       <c r="B412" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C412" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D412">
         <v>4</v>
@@ -10970,7 +10979,7 @@
         <v>53</v>
       </c>
       <c r="C413" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D413">
         <v>2</v>
@@ -10993,7 +11002,7 @@
         <v>64</v>
       </c>
       <c r="C414" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D414">
         <v>3</v>
@@ -11013,10 +11022,10 @@
         <v>46008</v>
       </c>
       <c r="B415" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C415" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D415">
         <v>3</v>
@@ -11036,10 +11045,10 @@
         <v>46008</v>
       </c>
       <c r="B416" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C416" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D416">
         <v>4</v>
@@ -11059,10 +11068,10 @@
         <v>46008</v>
       </c>
       <c r="B417" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C417" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D417">
         <v>4</v>
@@ -11085,7 +11094,7 @@
         <v>52</v>
       </c>
       <c r="C418" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D418">
         <v>3</v>
@@ -11105,10 +11114,10 @@
         <v>46008</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C419" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D419">
         <v>3</v>
@@ -11128,10 +11137,10 @@
         <v>46012</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C420" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D420">
         <v>1</v>
@@ -11151,10 +11160,10 @@
         <v>46012</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C421" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D421">
         <v>3</v>
@@ -11174,10 +11183,10 @@
         <v>46012</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C422" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D422">
         <v>3</v>
@@ -11197,10 +11206,10 @@
         <v>46012</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C423" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D423">
         <v>3</v>
@@ -11223,7 +11232,7 @@
         <v>30</v>
       </c>
       <c r="C424" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D424">
         <v>4</v>
@@ -11246,7 +11255,7 @@
         <v>64</v>
       </c>
       <c r="C425" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D425">
         <v>3</v>
@@ -11266,10 +11275,10 @@
         <v>46012</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C426" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D426">
         <v>3</v>
@@ -11282,6 +11291,397 @@
       </c>
       <c r="G426" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="427" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A427" s="1">
+        <v>46017</v>
+      </c>
+      <c r="B427" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C427" t="s">
+        <v>106</v>
+      </c>
+      <c r="D427">
+        <v>1</v>
+      </c>
+      <c r="E427">
+        <v>10</v>
+      </c>
+      <c r="F427">
+        <v>0</v>
+      </c>
+      <c r="G427" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="428" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A428" s="1">
+        <v>46017</v>
+      </c>
+      <c r="B428" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C428" t="s">
+        <v>106</v>
+      </c>
+      <c r="D428">
+        <v>1</v>
+      </c>
+      <c r="E428">
+        <v>10</v>
+      </c>
+      <c r="F428">
+        <v>0</v>
+      </c>
+      <c r="G428" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="429" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A429" s="1">
+        <v>46017</v>
+      </c>
+      <c r="B429" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C429" t="s">
+        <v>106</v>
+      </c>
+      <c r="D429">
+        <v>1</v>
+      </c>
+      <c r="E429">
+        <v>10</v>
+      </c>
+      <c r="F429">
+        <v>0</v>
+      </c>
+      <c r="G429" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="430" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A430" s="1">
+        <v>46017</v>
+      </c>
+      <c r="B430" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C430" t="s">
+        <v>99</v>
+      </c>
+      <c r="D430">
+        <v>4</v>
+      </c>
+      <c r="E430">
+        <v>30</v>
+      </c>
+      <c r="F430">
+        <v>0</v>
+      </c>
+      <c r="G430" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="431" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A431" s="1">
+        <v>46017</v>
+      </c>
+      <c r="B431" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C431" t="s">
+        <v>105</v>
+      </c>
+      <c r="D431">
+        <v>3</v>
+      </c>
+      <c r="E431">
+        <v>40</v>
+      </c>
+      <c r="F431">
+        <v>0</v>
+      </c>
+      <c r="G431" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="432" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A432" s="1">
+        <v>46017</v>
+      </c>
+      <c r="B432" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C432" t="s">
+        <v>105</v>
+      </c>
+      <c r="D432">
+        <v>3</v>
+      </c>
+      <c r="E432">
+        <v>20</v>
+      </c>
+      <c r="F432">
+        <v>0</v>
+      </c>
+      <c r="G432" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="433" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A433" s="1">
+        <v>46017</v>
+      </c>
+      <c r="B433" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C433" t="s">
+        <v>99</v>
+      </c>
+      <c r="D433">
+        <v>4</v>
+      </c>
+      <c r="E433">
+        <v>3</v>
+      </c>
+      <c r="F433">
+        <v>0</v>
+      </c>
+      <c r="G433" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="434" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A434" s="1">
+        <v>46017</v>
+      </c>
+      <c r="B434" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C434" t="s">
+        <v>99</v>
+      </c>
+      <c r="D434">
+        <v>4</v>
+      </c>
+      <c r="E434">
+        <v>6</v>
+      </c>
+      <c r="F434">
+        <v>0</v>
+      </c>
+      <c r="G434" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="435" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A435" s="1">
+        <v>46017</v>
+      </c>
+      <c r="B435" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C435" t="s">
+        <v>105</v>
+      </c>
+      <c r="D435">
+        <v>2</v>
+      </c>
+      <c r="E435">
+        <v>15</v>
+      </c>
+      <c r="F435">
+        <v>7.5</v>
+      </c>
+      <c r="G435" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="436" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A436" s="1">
+        <v>46018</v>
+      </c>
+      <c r="B436" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C436" t="s">
+        <v>106</v>
+      </c>
+      <c r="D436">
+        <v>1</v>
+      </c>
+      <c r="E436">
+        <v>12</v>
+      </c>
+      <c r="F436">
+        <v>0</v>
+      </c>
+      <c r="G436" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="437" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A437" s="1">
+        <v>46018</v>
+      </c>
+      <c r="B437" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C437" t="s">
+        <v>106</v>
+      </c>
+      <c r="D437">
+        <v>1</v>
+      </c>
+      <c r="E437">
+        <v>12</v>
+      </c>
+      <c r="F437">
+        <v>0</v>
+      </c>
+      <c r="G437" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="438" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A438" s="1">
+        <v>46018</v>
+      </c>
+      <c r="B438" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C438" t="s">
+        <v>106</v>
+      </c>
+      <c r="D438">
+        <v>1</v>
+      </c>
+      <c r="E438">
+        <v>10</v>
+      </c>
+      <c r="F438">
+        <v>0</v>
+      </c>
+      <c r="G438" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="439" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A439" s="1">
+        <v>46018</v>
+      </c>
+      <c r="B439" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C439" t="s">
+        <v>99</v>
+      </c>
+      <c r="D439">
+        <v>3</v>
+      </c>
+      <c r="E439">
+        <v>30</v>
+      </c>
+      <c r="F439">
+        <v>0</v>
+      </c>
+      <c r="G439" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="440" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A440" s="1">
+        <v>46018</v>
+      </c>
+      <c r="B440" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C440" t="s">
+        <v>105</v>
+      </c>
+      <c r="D440">
+        <v>3</v>
+      </c>
+      <c r="E440">
+        <v>15</v>
+      </c>
+      <c r="F440">
+        <v>0</v>
+      </c>
+      <c r="G440" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="441" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A441" s="1">
+        <v>46018</v>
+      </c>
+      <c r="B441" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C441" t="s">
+        <v>99</v>
+      </c>
+      <c r="D441">
+        <v>4</v>
+      </c>
+      <c r="E441">
+        <v>20</v>
+      </c>
+      <c r="F441">
+        <v>0</v>
+      </c>
+      <c r="G441" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="442" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A442" s="1">
+        <v>46018</v>
+      </c>
+      <c r="B442" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C442" t="s">
+        <v>104</v>
+      </c>
+      <c r="D442">
+        <v>3</v>
+      </c>
+      <c r="E442">
+        <v>20</v>
+      </c>
+      <c r="F442">
+        <v>20</v>
+      </c>
+      <c r="G442" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="443" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A443" s="1">
+        <v>46018</v>
+      </c>
+      <c r="B443" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C443" t="s">
+        <v>104</v>
+      </c>
+      <c r="D443">
+        <v>3</v>
+      </c>
+      <c r="E443">
+        <v>10</v>
+      </c>
+      <c r="F443">
+        <v>20</v>
+      </c>
+      <c r="G443" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -11318,16 +11718,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D1" t="s">
         <v>101</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>102</v>
-      </c>
-      <c r="D1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E1" t="s">
-        <v>104</v>
       </c>
       <c r="F1" t="s">
         <v>6</v>
@@ -11338,13 +11738,13 @@
         <v>45904</v>
       </c>
       <c r="B2" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D2" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E2">
         <v>10</v>
@@ -11355,13 +11755,13 @@
         <v>45904</v>
       </c>
       <c r="B3" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C3" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D3" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E3">
         <v>8</v>
@@ -11372,13 +11772,13 @@
         <v>45934</v>
       </c>
       <c r="B4" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C4" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D4" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E4">
         <v>10</v>
@@ -11389,13 +11789,13 @@
         <v>45934</v>
       </c>
       <c r="B5" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C5" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D5" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E5">
         <v>10</v>
@@ -11406,13 +11806,13 @@
         <v>45965</v>
       </c>
       <c r="B6" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C6" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D6" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E6">
         <v>10</v>
@@ -11423,13 +11823,13 @@
         <v>45965</v>
       </c>
       <c r="B7" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C7" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D7" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E7">
         <v>12</v>
@@ -11440,13 +11840,13 @@
         <v>45995</v>
       </c>
       <c r="B8" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C8" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D8" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E8">
         <v>8</v>
@@ -11457,13 +11857,13 @@
         <v>45995</v>
       </c>
       <c r="B9" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C9" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D9" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E9">
         <v>19</v>
@@ -11485,34 +11885,34 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/data_samples/workout_entry_template.xlsx
+++ b/data_samples/workout_entry_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amlim/Downloads/azure-fit-platform/data_samples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E7CCE6-9119-0F48-81D2-9A0F4F849670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98978BD8-9387-614B-B63C-35F326FA0BB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{5828482D-6AAB-A34A-A077-81D95F329610}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16100" xr2:uid="{5828482D-6AAB-A34A-A077-81D95F329610}"/>
   </bookViews>
   <sheets>
     <sheet name="workout_entry_template" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="212">
   <si>
     <t>date</t>
   </si>
@@ -594,12 +594,6 @@
     <t>Tuck Planche</t>
   </si>
   <si>
-    <t>Back Lever</t>
-  </si>
-  <si>
-    <t>Tuck Back Lever</t>
-  </si>
-  <si>
     <t>Seated Wall Angels (ER)</t>
   </si>
   <si>
@@ -634,6 +628,36 @@
   </si>
   <si>
     <t>Leg Swings</t>
+  </si>
+  <si>
+    <t>Alt. Tuck Planche Knee Lifts</t>
+  </si>
+  <si>
+    <t>Tuck Front Lever Raise</t>
+  </si>
+  <si>
+    <t>Could not do 20 reps anymore. Had to split it into sets of 10.</t>
+  </si>
+  <si>
+    <t>Seated Hip External Rotation</t>
+  </si>
+  <si>
+    <t>Pseudo Planche Tuck Slides</t>
+  </si>
+  <si>
+    <t>Front Lever</t>
+  </si>
+  <si>
+    <t>Tuck Front Lever</t>
+  </si>
+  <si>
+    <t>Hip Adductor Stretch</t>
+  </si>
+  <si>
+    <t>Seated Leg Curls</t>
+  </si>
+  <si>
+    <t>Band-Assisted Tuck Planche</t>
   </si>
 </sst>
 </file>
@@ -1504,7 +1528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09805D65-2793-1C46-AB3E-4E9435A12762}">
-  <dimension ref="A1:H472"/>
+  <dimension ref="A1:H573"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.6640625" customWidth="1"/>
@@ -1513,7 +1537,7 @@
     <col min="5" max="5" width="26.83203125" customWidth="1"/>
     <col min="6" max="6" width="17.5" customWidth="1"/>
     <col min="7" max="7" width="19.6640625" customWidth="1"/>
-    <col min="8" max="8" width="32.83203125" customWidth="1"/>
+    <col min="8" max="8" width="48.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
@@ -2907,7 +2931,7 @@
         <v>45901</v>
       </c>
       <c r="B61" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C61" t="s">
         <v>105</v>
@@ -2930,7 +2954,7 @@
         <v>45901</v>
       </c>
       <c r="B62" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C62" t="s">
         <v>105</v>
@@ -3574,7 +3598,7 @@
         <v>45910</v>
       </c>
       <c r="B90" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C90" t="s">
         <v>105</v>
@@ -3597,7 +3621,7 @@
         <v>45910</v>
       </c>
       <c r="B91" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C91" t="s">
         <v>105</v>
@@ -3620,7 +3644,7 @@
         <v>45910</v>
       </c>
       <c r="B92" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C92" t="s">
         <v>105</v>
@@ -4287,7 +4311,7 @@
         <v>45925</v>
       </c>
       <c r="B121" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C121" t="s">
         <v>105</v>
@@ -4310,7 +4334,7 @@
         <v>45925</v>
       </c>
       <c r="B122" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C122" t="s">
         <v>105</v>
@@ -4333,7 +4357,7 @@
         <v>45925</v>
       </c>
       <c r="B123" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C123" t="s">
         <v>105</v>
@@ -4931,7 +4955,7 @@
         <v>45929</v>
       </c>
       <c r="B149" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C149" t="s">
         <v>105</v>
@@ -4954,7 +4978,7 @@
         <v>45929</v>
       </c>
       <c r="B150" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C150" t="s">
         <v>105</v>
@@ -4977,7 +5001,7 @@
         <v>45929</v>
       </c>
       <c r="B151" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C151" t="s">
         <v>105</v>
@@ -5368,7 +5392,7 @@
         <v>45934</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C168" s="3" t="s">
         <v>105</v>
@@ -5392,7 +5416,7 @@
         <v>45934</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C169" s="3" t="s">
         <v>105</v>
@@ -5416,7 +5440,7 @@
         <v>45934</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C170" s="3" t="s">
         <v>105</v>
@@ -6153,7 +6177,7 @@
         <v>45953</v>
       </c>
       <c r="B202" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C202" t="s">
         <v>105</v>
@@ -6176,7 +6200,7 @@
         <v>45953</v>
       </c>
       <c r="B203" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C203" t="s">
         <v>105</v>
@@ -6199,7 +6223,7 @@
         <v>45953</v>
       </c>
       <c r="B204" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C204" t="s">
         <v>105</v>
@@ -6222,7 +6246,7 @@
         <v>45953</v>
       </c>
       <c r="B205" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C205" t="s">
         <v>98</v>
@@ -6245,7 +6269,7 @@
         <v>45953</v>
       </c>
       <c r="B206" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C206" t="s">
         <v>98</v>
@@ -6268,7 +6292,7 @@
         <v>45953</v>
       </c>
       <c r="B207" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C207" t="s">
         <v>98</v>
@@ -6636,7 +6660,7 @@
         <v>45958</v>
       </c>
       <c r="B223" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C223" t="s">
         <v>98</v>
@@ -7050,7 +7074,7 @@
         <v>45962</v>
       </c>
       <c r="B241" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C241" t="s">
         <v>98</v>
@@ -7257,7 +7281,7 @@
         <v>45967</v>
       </c>
       <c r="B250" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C250" t="s">
         <v>105</v>
@@ -7280,7 +7304,7 @@
         <v>45967</v>
       </c>
       <c r="B251" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C251" t="s">
         <v>105</v>
@@ -7303,7 +7327,7 @@
         <v>45967</v>
       </c>
       <c r="B252" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C252" t="s">
         <v>105</v>
@@ -7326,7 +7350,7 @@
         <v>45967</v>
       </c>
       <c r="B253" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C253" t="s">
         <v>105</v>
@@ -7464,7 +7488,7 @@
         <v>45967</v>
       </c>
       <c r="B259" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C259" t="s">
         <v>98</v>
@@ -7717,7 +7741,7 @@
         <v>45970</v>
       </c>
       <c r="B270" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C270" t="s">
         <v>103</v>
@@ -7970,7 +7994,7 @@
         <v>45973</v>
       </c>
       <c r="B281" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C281" t="s">
         <v>105</v>
@@ -7993,7 +8017,7 @@
         <v>45973</v>
       </c>
       <c r="B282" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C282" t="s">
         <v>105</v>
@@ -8016,7 +8040,7 @@
         <v>45973</v>
       </c>
       <c r="B283" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C283" t="s">
         <v>105</v>
@@ -8039,7 +8063,7 @@
         <v>45973</v>
       </c>
       <c r="B284" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C284" t="s">
         <v>105</v>
@@ -8177,7 +8201,7 @@
         <v>45973</v>
       </c>
       <c r="B290" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C290" t="s">
         <v>103</v>
@@ -8223,7 +8247,7 @@
         <v>45977</v>
       </c>
       <c r="B292" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C292" t="s">
         <v>105</v>
@@ -8246,7 +8270,7 @@
         <v>45977</v>
       </c>
       <c r="B293" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C293" t="s">
         <v>105</v>
@@ -8269,7 +8293,7 @@
         <v>45977</v>
       </c>
       <c r="B294" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C294" t="s">
         <v>105</v>
@@ -8292,7 +8316,7 @@
         <v>45977</v>
       </c>
       <c r="B295" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C295" t="s">
         <v>105</v>
@@ -9051,7 +9075,7 @@
         <v>45986</v>
       </c>
       <c r="B328" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C328" t="s">
         <v>103</v>
@@ -9258,7 +9282,7 @@
         <v>45990</v>
       </c>
       <c r="B337" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C337" t="s">
         <v>105</v>
@@ -9281,7 +9305,7 @@
         <v>45990</v>
       </c>
       <c r="B338" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C338" t="s">
         <v>105</v>
@@ -9626,7 +9650,7 @@
         <v>45991</v>
       </c>
       <c r="B353" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C353" t="s">
         <v>103</v>
@@ -9948,7 +9972,7 @@
         <v>45993</v>
       </c>
       <c r="B367" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C367" t="s">
         <v>103</v>
@@ -10477,7 +10501,7 @@
         <v>45998</v>
       </c>
       <c r="B390" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C390" t="s">
         <v>103</v>
@@ -12018,7 +12042,7 @@
         <v>46017</v>
       </c>
       <c r="B457" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C457" t="s">
         <v>105</v>
@@ -12041,7 +12065,7 @@
         <v>46017</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C458" t="s">
         <v>105</v>
@@ -12202,7 +12226,7 @@
         <v>46018</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C465" t="s">
         <v>105</v>
@@ -12225,7 +12249,7 @@
         <v>46018</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C466" t="s">
         <v>105</v>
@@ -12248,7 +12272,7 @@
         <v>46018</v>
       </c>
       <c r="B467" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C467" t="s">
         <v>105</v>
@@ -12317,7 +12341,7 @@
         <v>46018</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C470" t="s">
         <v>98</v>
@@ -12340,7 +12364,7 @@
         <v>46018</v>
       </c>
       <c r="B471" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C471" t="s">
         <v>103</v>
@@ -12363,7 +12387,7 @@
         <v>46018</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C472" t="s">
         <v>103</v>
@@ -12379,6 +12403,2332 @@
       </c>
       <c r="G472" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="473" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A473" s="1">
+        <v>46020</v>
+      </c>
+      <c r="B473" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C473" t="s">
+        <v>105</v>
+      </c>
+      <c r="D473">
+        <v>1</v>
+      </c>
+      <c r="E473">
+        <v>12</v>
+      </c>
+      <c r="F473">
+        <v>0</v>
+      </c>
+      <c r="G473" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="474" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A474" s="1">
+        <v>46020</v>
+      </c>
+      <c r="B474" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C474" t="s">
+        <v>105</v>
+      </c>
+      <c r="D474">
+        <v>1</v>
+      </c>
+      <c r="E474">
+        <v>12</v>
+      </c>
+      <c r="F474">
+        <v>0</v>
+      </c>
+      <c r="G474" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="475" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A475" s="1">
+        <v>46020</v>
+      </c>
+      <c r="B475" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C475" t="s">
+        <v>105</v>
+      </c>
+      <c r="D475">
+        <v>1</v>
+      </c>
+      <c r="E475">
+        <v>12</v>
+      </c>
+      <c r="F475">
+        <v>0</v>
+      </c>
+      <c r="G475" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="476" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A476" s="1">
+        <v>46020</v>
+      </c>
+      <c r="B476" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C476" t="s">
+        <v>98</v>
+      </c>
+      <c r="D476">
+        <v>4</v>
+      </c>
+      <c r="E476">
+        <v>30</v>
+      </c>
+      <c r="F476">
+        <v>0</v>
+      </c>
+      <c r="G476" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="477" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A477" s="1">
+        <v>46020</v>
+      </c>
+      <c r="B477" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C477" t="s">
+        <v>98</v>
+      </c>
+      <c r="D477">
+        <v>4</v>
+      </c>
+      <c r="E477">
+        <v>15</v>
+      </c>
+      <c r="F477">
+        <v>0</v>
+      </c>
+      <c r="G477" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="478" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A478" s="1">
+        <v>46020</v>
+      </c>
+      <c r="B478" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C478" t="s">
+        <v>104</v>
+      </c>
+      <c r="D478">
+        <v>3</v>
+      </c>
+      <c r="E478">
+        <v>15</v>
+      </c>
+      <c r="F478">
+        <v>0</v>
+      </c>
+      <c r="G478" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="479" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A479" s="1">
+        <v>46020</v>
+      </c>
+      <c r="B479" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C479" t="s">
+        <v>98</v>
+      </c>
+      <c r="D479">
+        <v>3</v>
+      </c>
+      <c r="E479">
+        <v>6</v>
+      </c>
+      <c r="F479">
+        <v>0</v>
+      </c>
+      <c r="G479" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="480" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A480" s="1">
+        <v>46020</v>
+      </c>
+      <c r="B480" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C480" t="s">
+        <v>103</v>
+      </c>
+      <c r="D480">
+        <v>5</v>
+      </c>
+      <c r="E480">
+        <v>5</v>
+      </c>
+      <c r="F480">
+        <v>0</v>
+      </c>
+      <c r="G480" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="481" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A481" s="1">
+        <v>46020</v>
+      </c>
+      <c r="B481" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C481" t="s">
+        <v>103</v>
+      </c>
+      <c r="D481">
+        <v>3</v>
+      </c>
+      <c r="E481">
+        <v>10</v>
+      </c>
+      <c r="F481">
+        <v>20</v>
+      </c>
+      <c r="G481" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="482" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A482" s="1">
+        <v>46020</v>
+      </c>
+      <c r="B482" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C482" t="s">
+        <v>103</v>
+      </c>
+      <c r="D482">
+        <v>4</v>
+      </c>
+      <c r="E482">
+        <v>6</v>
+      </c>
+      <c r="F482">
+        <v>0</v>
+      </c>
+      <c r="G482" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="483" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A483" s="1">
+        <v>46020</v>
+      </c>
+      <c r="B483" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C483" t="s">
+        <v>103</v>
+      </c>
+      <c r="D483">
+        <v>4</v>
+      </c>
+      <c r="E483">
+        <v>10</v>
+      </c>
+      <c r="F483">
+        <v>0</v>
+      </c>
+      <c r="G483" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="484" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A484" s="1">
+        <v>46020</v>
+      </c>
+      <c r="B484" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C484" t="s">
+        <v>104</v>
+      </c>
+      <c r="D484">
+        <v>2</v>
+      </c>
+      <c r="E484">
+        <v>30</v>
+      </c>
+      <c r="F484">
+        <v>0</v>
+      </c>
+      <c r="G484" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="485" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A485" s="1">
+        <v>46020</v>
+      </c>
+      <c r="B485" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C485" t="s">
+        <v>103</v>
+      </c>
+      <c r="D485">
+        <v>2</v>
+      </c>
+      <c r="E485">
+        <v>20</v>
+      </c>
+      <c r="F485">
+        <v>40</v>
+      </c>
+      <c r="G485" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="486" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A486" s="1">
+        <v>46020</v>
+      </c>
+      <c r="B486" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C486" t="s">
+        <v>103</v>
+      </c>
+      <c r="D486">
+        <v>2</v>
+      </c>
+      <c r="E486">
+        <v>10</v>
+      </c>
+      <c r="F486">
+        <v>40</v>
+      </c>
+      <c r="G486" t="s">
+        <v>8</v>
+      </c>
+      <c r="H486" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="487" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A487" s="1">
+        <v>46022</v>
+      </c>
+      <c r="B487" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C487" t="s">
+        <v>105</v>
+      </c>
+      <c r="D487">
+        <v>1</v>
+      </c>
+      <c r="E487">
+        <v>15</v>
+      </c>
+      <c r="F487">
+        <v>0</v>
+      </c>
+      <c r="G487" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="488" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A488" s="1">
+        <v>46022</v>
+      </c>
+      <c r="B488" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C488" t="s">
+        <v>105</v>
+      </c>
+      <c r="D488">
+        <v>1</v>
+      </c>
+      <c r="E488">
+        <v>15</v>
+      </c>
+      <c r="F488">
+        <v>0</v>
+      </c>
+      <c r="G488" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="489" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A489" s="1">
+        <v>46022</v>
+      </c>
+      <c r="B489" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C489" t="s">
+        <v>105</v>
+      </c>
+      <c r="D489">
+        <v>1</v>
+      </c>
+      <c r="E489">
+        <v>10</v>
+      </c>
+      <c r="F489">
+        <v>0</v>
+      </c>
+      <c r="G489" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="490" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A490" s="1">
+        <v>46022</v>
+      </c>
+      <c r="B490" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C490" t="s">
+        <v>105</v>
+      </c>
+      <c r="D490">
+        <v>1</v>
+      </c>
+      <c r="E490">
+        <v>5</v>
+      </c>
+      <c r="F490">
+        <v>0</v>
+      </c>
+      <c r="G490" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="491" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A491" s="1">
+        <v>46022</v>
+      </c>
+      <c r="B491" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C491" t="s">
+        <v>98</v>
+      </c>
+      <c r="D491">
+        <v>3</v>
+      </c>
+      <c r="E491">
+        <v>30</v>
+      </c>
+      <c r="F491">
+        <v>0</v>
+      </c>
+      <c r="G491" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="492" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A492" s="1">
+        <v>46022</v>
+      </c>
+      <c r="B492" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C492" t="s">
+        <v>103</v>
+      </c>
+      <c r="D492">
+        <v>4</v>
+      </c>
+      <c r="E492">
+        <v>15</v>
+      </c>
+      <c r="F492">
+        <v>0</v>
+      </c>
+      <c r="G492" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="493" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A493" s="1">
+        <v>46022</v>
+      </c>
+      <c r="B493" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C493" t="s">
+        <v>103</v>
+      </c>
+      <c r="D493">
+        <v>3</v>
+      </c>
+      <c r="E493">
+        <v>20</v>
+      </c>
+      <c r="F493">
+        <v>20</v>
+      </c>
+      <c r="G493" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="494" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A494" s="1">
+        <v>46022</v>
+      </c>
+      <c r="B494" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C494" t="s">
+        <v>105</v>
+      </c>
+      <c r="D494">
+        <v>1</v>
+      </c>
+      <c r="E494">
+        <v>10</v>
+      </c>
+      <c r="F494">
+        <v>0</v>
+      </c>
+      <c r="G494" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="495" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A495" s="1">
+        <v>46022</v>
+      </c>
+      <c r="B495" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C495" t="s">
+        <v>105</v>
+      </c>
+      <c r="D495">
+        <v>1</v>
+      </c>
+      <c r="E495">
+        <v>10</v>
+      </c>
+      <c r="F495">
+        <v>0</v>
+      </c>
+      <c r="G495" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="496" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A496" s="1">
+        <v>46026</v>
+      </c>
+      <c r="B496" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C496" t="s">
+        <v>105</v>
+      </c>
+      <c r="D496">
+        <v>1</v>
+      </c>
+      <c r="E496">
+        <v>10</v>
+      </c>
+      <c r="F496">
+        <v>0</v>
+      </c>
+      <c r="G496" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="497" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A497" s="1">
+        <v>46026</v>
+      </c>
+      <c r="B497" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C497" t="s">
+        <v>105</v>
+      </c>
+      <c r="D497">
+        <v>1</v>
+      </c>
+      <c r="E497">
+        <v>10</v>
+      </c>
+      <c r="F497">
+        <v>0</v>
+      </c>
+      <c r="G497" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="498" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A498" s="1">
+        <v>46026</v>
+      </c>
+      <c r="B498" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C498" t="s">
+        <v>105</v>
+      </c>
+      <c r="D498">
+        <v>1</v>
+      </c>
+      <c r="E498">
+        <v>15</v>
+      </c>
+      <c r="F498">
+        <v>0</v>
+      </c>
+      <c r="G498" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="499" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A499" s="1">
+        <v>46026</v>
+      </c>
+      <c r="B499" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C499" t="s">
+        <v>105</v>
+      </c>
+      <c r="D499">
+        <v>1</v>
+      </c>
+      <c r="E499">
+        <v>10</v>
+      </c>
+      <c r="F499">
+        <v>0</v>
+      </c>
+      <c r="G499" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="500" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A500" s="1">
+        <v>46026</v>
+      </c>
+      <c r="B500" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C500" t="s">
+        <v>105</v>
+      </c>
+      <c r="D500">
+        <v>2</v>
+      </c>
+      <c r="E500">
+        <v>15</v>
+      </c>
+      <c r="F500">
+        <v>0</v>
+      </c>
+      <c r="G500" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="501" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A501" s="1">
+        <v>46026</v>
+      </c>
+      <c r="B501" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C501" t="s">
+        <v>105</v>
+      </c>
+      <c r="D501">
+        <v>2</v>
+      </c>
+      <c r="E501">
+        <v>15</v>
+      </c>
+      <c r="F501">
+        <v>0</v>
+      </c>
+      <c r="G501" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="502" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A502" s="1">
+        <v>46026</v>
+      </c>
+      <c r="B502" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C502" t="s">
+        <v>98</v>
+      </c>
+      <c r="D502">
+        <v>2</v>
+      </c>
+      <c r="E502">
+        <v>40</v>
+      </c>
+      <c r="F502">
+        <v>0</v>
+      </c>
+      <c r="G502" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="503" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A503" s="1">
+        <v>46026</v>
+      </c>
+      <c r="B503" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C503" t="s">
+        <v>104</v>
+      </c>
+      <c r="D503">
+        <v>3</v>
+      </c>
+      <c r="E503">
+        <v>30</v>
+      </c>
+      <c r="F503">
+        <v>0</v>
+      </c>
+      <c r="G503" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="504" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A504" s="1">
+        <v>46026</v>
+      </c>
+      <c r="B504" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C504" t="s">
+        <v>103</v>
+      </c>
+      <c r="D504">
+        <v>4</v>
+      </c>
+      <c r="E504">
+        <v>10</v>
+      </c>
+      <c r="F504">
+        <v>275</v>
+      </c>
+      <c r="G504" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="505" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A505" s="1">
+        <v>46026</v>
+      </c>
+      <c r="B505" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C505" t="s">
+        <v>98</v>
+      </c>
+      <c r="D505">
+        <v>3</v>
+      </c>
+      <c r="E505">
+        <v>30</v>
+      </c>
+      <c r="F505">
+        <v>0</v>
+      </c>
+      <c r="G505" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="506" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A506" s="1">
+        <v>46026</v>
+      </c>
+      <c r="B506" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C506" t="s">
+        <v>103</v>
+      </c>
+      <c r="D506">
+        <v>3</v>
+      </c>
+      <c r="E506">
+        <v>10</v>
+      </c>
+      <c r="F506">
+        <v>115</v>
+      </c>
+      <c r="G506" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="507" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A507" s="1">
+        <v>46026</v>
+      </c>
+      <c r="B507" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C507" t="s">
+        <v>103</v>
+      </c>
+      <c r="D507">
+        <v>3</v>
+      </c>
+      <c r="E507">
+        <v>6</v>
+      </c>
+      <c r="F507">
+        <v>0</v>
+      </c>
+      <c r="G507" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="508" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A508" s="1">
+        <v>46026</v>
+      </c>
+      <c r="B508" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C508" t="s">
+        <v>103</v>
+      </c>
+      <c r="D508">
+        <v>2</v>
+      </c>
+      <c r="E508">
+        <v>6</v>
+      </c>
+      <c r="F508">
+        <v>45</v>
+      </c>
+      <c r="G508" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="509" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A509" s="1">
+        <v>46027</v>
+      </c>
+      <c r="B509" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C509" t="s">
+        <v>105</v>
+      </c>
+      <c r="D509">
+        <v>2</v>
+      </c>
+      <c r="E509">
+        <v>15</v>
+      </c>
+      <c r="F509">
+        <v>0</v>
+      </c>
+      <c r="G509" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="510" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A510" s="1">
+        <v>46027</v>
+      </c>
+      <c r="B510" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C510" t="s">
+        <v>105</v>
+      </c>
+      <c r="D510">
+        <v>2</v>
+      </c>
+      <c r="E510">
+        <v>15</v>
+      </c>
+      <c r="F510">
+        <v>0</v>
+      </c>
+      <c r="G510" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="511" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A511" s="1">
+        <v>46027</v>
+      </c>
+      <c r="B511" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C511" t="s">
+        <v>105</v>
+      </c>
+      <c r="D511">
+        <v>1</v>
+      </c>
+      <c r="E511">
+        <v>10</v>
+      </c>
+      <c r="F511">
+        <v>0</v>
+      </c>
+      <c r="G511" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="512" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A512" s="1">
+        <v>46027</v>
+      </c>
+      <c r="B512" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C512" t="s">
+        <v>105</v>
+      </c>
+      <c r="D512">
+        <v>1</v>
+      </c>
+      <c r="E512">
+        <v>15</v>
+      </c>
+      <c r="F512">
+        <v>0</v>
+      </c>
+      <c r="G512" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="513" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A513" s="1">
+        <v>46027</v>
+      </c>
+      <c r="B513" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C513" t="s">
+        <v>104</v>
+      </c>
+      <c r="D513">
+        <v>4</v>
+      </c>
+      <c r="E513">
+        <v>15</v>
+      </c>
+      <c r="F513">
+        <v>0</v>
+      </c>
+      <c r="G513" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="514" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A514" s="1">
+        <v>46027</v>
+      </c>
+      <c r="B514" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C514" t="s">
+        <v>103</v>
+      </c>
+      <c r="D514">
+        <v>1</v>
+      </c>
+      <c r="E514">
+        <v>15</v>
+      </c>
+      <c r="F514">
+        <v>12.5</v>
+      </c>
+      <c r="G514" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="515" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A515" s="1">
+        <v>46027</v>
+      </c>
+      <c r="B515" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C515" t="s">
+        <v>103</v>
+      </c>
+      <c r="D515">
+        <v>1</v>
+      </c>
+      <c r="E515">
+        <v>15</v>
+      </c>
+      <c r="F515">
+        <v>12.5</v>
+      </c>
+      <c r="G515" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="516" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A516" s="1">
+        <v>46027</v>
+      </c>
+      <c r="B516" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C516" t="s">
+        <v>103</v>
+      </c>
+      <c r="D516">
+        <v>1</v>
+      </c>
+      <c r="E516">
+        <v>15</v>
+      </c>
+      <c r="F516">
+        <v>12.5</v>
+      </c>
+      <c r="G516" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="517" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A517" s="1">
+        <v>46027</v>
+      </c>
+      <c r="B517" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C517" t="s">
+        <v>98</v>
+      </c>
+      <c r="D517">
+        <v>3</v>
+      </c>
+      <c r="E517">
+        <v>3</v>
+      </c>
+      <c r="F517">
+        <v>0</v>
+      </c>
+      <c r="G517" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="518" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A518" s="1">
+        <v>46027</v>
+      </c>
+      <c r="B518" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C518" t="s">
+        <v>98</v>
+      </c>
+      <c r="D518">
+        <v>2</v>
+      </c>
+      <c r="E518">
+        <v>6</v>
+      </c>
+      <c r="F518">
+        <v>0</v>
+      </c>
+      <c r="G518" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="519" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A519" s="1">
+        <v>46027</v>
+      </c>
+      <c r="B519" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C519" t="s">
+        <v>103</v>
+      </c>
+      <c r="D519">
+        <v>4</v>
+      </c>
+      <c r="E519">
+        <v>6</v>
+      </c>
+      <c r="F519">
+        <v>25</v>
+      </c>
+      <c r="G519" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="520" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A520" s="1">
+        <v>46027</v>
+      </c>
+      <c r="B520" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C520" t="s">
+        <v>104</v>
+      </c>
+      <c r="D520">
+        <v>3</v>
+      </c>
+      <c r="E520">
+        <v>10</v>
+      </c>
+      <c r="F520">
+        <v>0</v>
+      </c>
+      <c r="G520" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="521" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A521" s="1">
+        <v>46027</v>
+      </c>
+      <c r="B521" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C521" t="s">
+        <v>103</v>
+      </c>
+      <c r="D521">
+        <v>3</v>
+      </c>
+      <c r="E521">
+        <v>10</v>
+      </c>
+      <c r="F521">
+        <v>0</v>
+      </c>
+      <c r="G521" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="522" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A522" s="1">
+        <v>46029</v>
+      </c>
+      <c r="B522" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C522" t="s">
+        <v>105</v>
+      </c>
+      <c r="D522">
+        <v>1</v>
+      </c>
+      <c r="E522">
+        <v>12</v>
+      </c>
+      <c r="F522">
+        <v>0</v>
+      </c>
+      <c r="G522" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="523" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A523" s="1">
+        <v>46029</v>
+      </c>
+      <c r="B523" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C523" t="s">
+        <v>105</v>
+      </c>
+      <c r="D523">
+        <v>1</v>
+      </c>
+      <c r="E523">
+        <v>12</v>
+      </c>
+      <c r="F523">
+        <v>0</v>
+      </c>
+      <c r="G523" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="524" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A524" s="1">
+        <v>46029</v>
+      </c>
+      <c r="B524" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C524" t="s">
+        <v>105</v>
+      </c>
+      <c r="D524">
+        <v>1</v>
+      </c>
+      <c r="E524">
+        <v>12</v>
+      </c>
+      <c r="F524">
+        <v>0</v>
+      </c>
+      <c r="G524" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="525" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A525" s="1">
+        <v>46029</v>
+      </c>
+      <c r="B525" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C525" t="s">
+        <v>105</v>
+      </c>
+      <c r="D525">
+        <v>2</v>
+      </c>
+      <c r="E525">
+        <v>15</v>
+      </c>
+      <c r="F525">
+        <v>0</v>
+      </c>
+      <c r="G525" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="526" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A526" s="1">
+        <v>46029</v>
+      </c>
+      <c r="B526" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C526" t="s">
+        <v>105</v>
+      </c>
+      <c r="D526">
+        <v>2</v>
+      </c>
+      <c r="E526">
+        <v>15</v>
+      </c>
+      <c r="F526">
+        <v>0</v>
+      </c>
+      <c r="G526" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="527" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A527" s="1">
+        <v>46029</v>
+      </c>
+      <c r="B527" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C527" t="s">
+        <v>98</v>
+      </c>
+      <c r="D527">
+        <v>2</v>
+      </c>
+      <c r="E527">
+        <v>6</v>
+      </c>
+      <c r="F527">
+        <v>0</v>
+      </c>
+      <c r="G527" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="528" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A528" s="1">
+        <v>46029</v>
+      </c>
+      <c r="B528" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C528" t="s">
+        <v>98</v>
+      </c>
+      <c r="D528">
+        <v>3</v>
+      </c>
+      <c r="E528">
+        <v>35</v>
+      </c>
+      <c r="F528">
+        <v>0</v>
+      </c>
+      <c r="G528" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="529" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A529" s="1">
+        <v>46029</v>
+      </c>
+      <c r="B529" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C529" t="s">
+        <v>98</v>
+      </c>
+      <c r="D529">
+        <v>3</v>
+      </c>
+      <c r="E529">
+        <v>30</v>
+      </c>
+      <c r="F529">
+        <v>0</v>
+      </c>
+      <c r="G529" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="530" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A530" s="1">
+        <v>46029</v>
+      </c>
+      <c r="B530" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C530" t="s">
+        <v>104</v>
+      </c>
+      <c r="D530">
+        <v>3</v>
+      </c>
+      <c r="E530">
+        <v>10</v>
+      </c>
+      <c r="F530">
+        <v>0</v>
+      </c>
+      <c r="G530" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="531" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A531" s="1">
+        <v>46029</v>
+      </c>
+      <c r="B531" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C531" t="s">
+        <v>103</v>
+      </c>
+      <c r="D531">
+        <v>4</v>
+      </c>
+      <c r="E531">
+        <v>8</v>
+      </c>
+      <c r="F531">
+        <v>25</v>
+      </c>
+      <c r="G531" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="532" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A532" s="1">
+        <v>46029</v>
+      </c>
+      <c r="B532" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C532" t="s">
+        <v>103</v>
+      </c>
+      <c r="D532">
+        <v>3</v>
+      </c>
+      <c r="E532">
+        <v>6</v>
+      </c>
+      <c r="F532">
+        <v>0</v>
+      </c>
+      <c r="G532" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="533" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A533" s="1">
+        <v>46029</v>
+      </c>
+      <c r="B533" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C533" t="s">
+        <v>103</v>
+      </c>
+      <c r="D533">
+        <v>1</v>
+      </c>
+      <c r="E533">
+        <v>10</v>
+      </c>
+      <c r="F533">
+        <v>45</v>
+      </c>
+      <c r="G533" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="534" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A534" s="1">
+        <v>46029</v>
+      </c>
+      <c r="B534" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C534" t="s">
+        <v>103</v>
+      </c>
+      <c r="D534">
+        <v>2</v>
+      </c>
+      <c r="E534">
+        <v>6</v>
+      </c>
+      <c r="F534">
+        <v>70</v>
+      </c>
+      <c r="G534" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="535" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A535" s="1">
+        <v>46034</v>
+      </c>
+      <c r="B535" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C535" t="s">
+        <v>105</v>
+      </c>
+      <c r="D535">
+        <v>2</v>
+      </c>
+      <c r="E535">
+        <v>15</v>
+      </c>
+      <c r="F535">
+        <v>0</v>
+      </c>
+      <c r="G535" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="536" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A536" s="1">
+        <v>46034</v>
+      </c>
+      <c r="B536" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C536" t="s">
+        <v>105</v>
+      </c>
+      <c r="D536">
+        <v>2</v>
+      </c>
+      <c r="E536">
+        <v>15</v>
+      </c>
+      <c r="F536">
+        <v>0</v>
+      </c>
+      <c r="G536" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="537" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A537" s="1">
+        <v>46034</v>
+      </c>
+      <c r="B537" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C537" t="s">
+        <v>98</v>
+      </c>
+      <c r="D537">
+        <v>3</v>
+      </c>
+      <c r="E537">
+        <v>35</v>
+      </c>
+      <c r="F537">
+        <v>0</v>
+      </c>
+      <c r="G537" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="538" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A538" s="1">
+        <v>46034</v>
+      </c>
+      <c r="B538" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C538" t="s">
+        <v>103</v>
+      </c>
+      <c r="D538">
+        <v>2</v>
+      </c>
+      <c r="E538">
+        <v>15</v>
+      </c>
+      <c r="F538">
+        <v>15</v>
+      </c>
+      <c r="G538" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="539" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A539" s="1">
+        <v>46034</v>
+      </c>
+      <c r="B539" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C539" t="s">
+        <v>103</v>
+      </c>
+      <c r="D539">
+        <v>2</v>
+      </c>
+      <c r="E539">
+        <v>15</v>
+      </c>
+      <c r="F539">
+        <v>15</v>
+      </c>
+      <c r="G539" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="540" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A540" s="1">
+        <v>46034</v>
+      </c>
+      <c r="B540" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C540" t="s">
+        <v>103</v>
+      </c>
+      <c r="D540">
+        <v>2</v>
+      </c>
+      <c r="E540">
+        <v>15</v>
+      </c>
+      <c r="F540">
+        <v>15</v>
+      </c>
+      <c r="G540" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="541" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A541" s="1">
+        <v>46034</v>
+      </c>
+      <c r="B541" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C541" t="s">
+        <v>98</v>
+      </c>
+      <c r="D541">
+        <v>2</v>
+      </c>
+      <c r="E541">
+        <v>6</v>
+      </c>
+      <c r="F541">
+        <v>0</v>
+      </c>
+      <c r="G541" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="542" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A542" s="1">
+        <v>46034</v>
+      </c>
+      <c r="B542" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C542" t="s">
+        <v>103</v>
+      </c>
+      <c r="D542">
+        <v>3</v>
+      </c>
+      <c r="E542">
+        <v>10</v>
+      </c>
+      <c r="F542">
+        <v>40</v>
+      </c>
+      <c r="G542" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="543" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A543" s="1">
+        <v>46036</v>
+      </c>
+      <c r="B543" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C543" t="s">
+        <v>105</v>
+      </c>
+      <c r="D543">
+        <v>1</v>
+      </c>
+      <c r="E543">
+        <v>15</v>
+      </c>
+      <c r="F543">
+        <v>0</v>
+      </c>
+      <c r="G543" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="544" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A544" s="1">
+        <v>46036</v>
+      </c>
+      <c r="B544" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C544" t="s">
+        <v>105</v>
+      </c>
+      <c r="D544">
+        <v>1</v>
+      </c>
+      <c r="E544">
+        <v>10</v>
+      </c>
+      <c r="F544">
+        <v>0</v>
+      </c>
+      <c r="G544" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="545" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A545" s="1">
+        <v>46036</v>
+      </c>
+      <c r="B545" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C545" t="s">
+        <v>105</v>
+      </c>
+      <c r="D545">
+        <v>2</v>
+      </c>
+      <c r="E545">
+        <v>15</v>
+      </c>
+      <c r="F545">
+        <v>0</v>
+      </c>
+      <c r="G545" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="546" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A546" s="1">
+        <v>46036</v>
+      </c>
+      <c r="B546" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C546" t="s">
+        <v>105</v>
+      </c>
+      <c r="D546">
+        <v>2</v>
+      </c>
+      <c r="E546">
+        <v>15</v>
+      </c>
+      <c r="F546">
+        <v>0</v>
+      </c>
+      <c r="G546" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="547" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A547" s="1">
+        <v>46036</v>
+      </c>
+      <c r="B547" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C547" t="s">
+        <v>98</v>
+      </c>
+      <c r="D547">
+        <v>4</v>
+      </c>
+      <c r="E547">
+        <v>30</v>
+      </c>
+      <c r="F547">
+        <v>0</v>
+      </c>
+      <c r="G547" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="548" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A548" s="1">
+        <v>46036</v>
+      </c>
+      <c r="B548" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C548" t="s">
+        <v>103</v>
+      </c>
+      <c r="D548">
+        <v>4</v>
+      </c>
+      <c r="E548">
+        <v>25</v>
+      </c>
+      <c r="F548">
+        <v>0</v>
+      </c>
+      <c r="G548" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="549" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A549" s="1">
+        <v>46036</v>
+      </c>
+      <c r="B549" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C549" t="s">
+        <v>104</v>
+      </c>
+      <c r="D549">
+        <v>3</v>
+      </c>
+      <c r="E549">
+        <v>15</v>
+      </c>
+      <c r="F549">
+        <v>0</v>
+      </c>
+      <c r="G549" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="550" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A550" s="1">
+        <v>46036</v>
+      </c>
+      <c r="B550" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C550" t="s">
+        <v>103</v>
+      </c>
+      <c r="D550">
+        <v>4</v>
+      </c>
+      <c r="E550">
+        <v>12</v>
+      </c>
+      <c r="F550">
+        <v>20</v>
+      </c>
+      <c r="G550" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="551" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A551" s="1">
+        <v>46036</v>
+      </c>
+      <c r="B551" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C551" t="s">
+        <v>104</v>
+      </c>
+      <c r="D551">
+        <v>3</v>
+      </c>
+      <c r="E551">
+        <v>25</v>
+      </c>
+      <c r="F551">
+        <v>0</v>
+      </c>
+      <c r="G551" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="552" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A552" s="1">
+        <v>46036</v>
+      </c>
+      <c r="B552" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C552" t="s">
+        <v>103</v>
+      </c>
+      <c r="D552">
+        <v>3</v>
+      </c>
+      <c r="E552">
+        <v>6</v>
+      </c>
+      <c r="F552">
+        <v>0</v>
+      </c>
+      <c r="G552" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="553" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A553" s="1">
+        <v>46036</v>
+      </c>
+      <c r="B553" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C553" t="s">
+        <v>103</v>
+      </c>
+      <c r="D553">
+        <v>3</v>
+      </c>
+      <c r="E553">
+        <v>6</v>
+      </c>
+      <c r="F553">
+        <v>40</v>
+      </c>
+      <c r="G553" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="554" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A554" s="1">
+        <v>46037</v>
+      </c>
+      <c r="B554" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C554" t="s">
+        <v>105</v>
+      </c>
+      <c r="D554">
+        <v>1</v>
+      </c>
+      <c r="E554">
+        <v>10</v>
+      </c>
+      <c r="F554">
+        <v>0</v>
+      </c>
+      <c r="G554" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="555" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A555" s="1">
+        <v>46037</v>
+      </c>
+      <c r="B555" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C555" t="s">
+        <v>105</v>
+      </c>
+      <c r="D555">
+        <v>1</v>
+      </c>
+      <c r="E555">
+        <v>10</v>
+      </c>
+      <c r="F555">
+        <v>0</v>
+      </c>
+      <c r="G555" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="556" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A556" s="1">
+        <v>46037</v>
+      </c>
+      <c r="B556" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C556" t="s">
+        <v>105</v>
+      </c>
+      <c r="D556">
+        <v>1</v>
+      </c>
+      <c r="E556">
+        <v>10</v>
+      </c>
+      <c r="F556">
+        <v>0</v>
+      </c>
+      <c r="G556" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="557" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A557" s="1">
+        <v>46037</v>
+      </c>
+      <c r="B557" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C557" t="s">
+        <v>105</v>
+      </c>
+      <c r="D557">
+        <v>1</v>
+      </c>
+      <c r="E557">
+        <v>10</v>
+      </c>
+      <c r="F557">
+        <v>0</v>
+      </c>
+      <c r="G557" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="558" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A558" s="1">
+        <v>46037</v>
+      </c>
+      <c r="B558" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C558" t="s">
+        <v>105</v>
+      </c>
+      <c r="D558">
+        <v>1</v>
+      </c>
+      <c r="E558">
+        <v>10</v>
+      </c>
+      <c r="F558">
+        <v>0</v>
+      </c>
+      <c r="G558" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="559" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A559" s="1">
+        <v>46037</v>
+      </c>
+      <c r="B559" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C559" t="s">
+        <v>103</v>
+      </c>
+      <c r="D559">
+        <v>4</v>
+      </c>
+      <c r="E559">
+        <v>10</v>
+      </c>
+      <c r="F559">
+        <v>35</v>
+      </c>
+      <c r="G559" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="560" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A560" s="1">
+        <v>46037</v>
+      </c>
+      <c r="B560" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C560" t="s">
+        <v>103</v>
+      </c>
+      <c r="D560">
+        <v>2</v>
+      </c>
+      <c r="E560">
+        <v>10</v>
+      </c>
+      <c r="F560">
+        <v>120</v>
+      </c>
+      <c r="G560" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="561" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A561" s="1">
+        <v>46037</v>
+      </c>
+      <c r="B561" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C561" t="s">
+        <v>103</v>
+      </c>
+      <c r="D561">
+        <v>2</v>
+      </c>
+      <c r="E561">
+        <v>8</v>
+      </c>
+      <c r="F561">
+        <v>140</v>
+      </c>
+      <c r="G561" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="562" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A562" s="1">
+        <v>46037</v>
+      </c>
+      <c r="B562" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C562" t="s">
+        <v>103</v>
+      </c>
+      <c r="D562">
+        <v>3</v>
+      </c>
+      <c r="E562">
+        <v>8</v>
+      </c>
+      <c r="F562">
+        <v>115</v>
+      </c>
+      <c r="G562" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="563" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A563" s="1">
+        <v>46037</v>
+      </c>
+      <c r="B563" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C563" t="s">
+        <v>103</v>
+      </c>
+      <c r="D563">
+        <v>2</v>
+      </c>
+      <c r="E563">
+        <v>13</v>
+      </c>
+      <c r="F563">
+        <v>70</v>
+      </c>
+      <c r="G563" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="564" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A564" s="1">
+        <v>46038</v>
+      </c>
+      <c r="B564" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C564" t="s">
+        <v>105</v>
+      </c>
+      <c r="D564">
+        <v>1</v>
+      </c>
+      <c r="E564">
+        <v>15</v>
+      </c>
+      <c r="F564">
+        <v>0</v>
+      </c>
+      <c r="G564" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="565" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A565" s="1">
+        <v>46038</v>
+      </c>
+      <c r="B565" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C565" t="s">
+        <v>105</v>
+      </c>
+      <c r="D565">
+        <v>1</v>
+      </c>
+      <c r="E565">
+        <v>15</v>
+      </c>
+      <c r="F565">
+        <v>0</v>
+      </c>
+      <c r="G565" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="566" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A566" s="1">
+        <v>46038</v>
+      </c>
+      <c r="B566" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C566" t="s">
+        <v>105</v>
+      </c>
+      <c r="D566">
+        <v>1</v>
+      </c>
+      <c r="E566">
+        <v>15</v>
+      </c>
+      <c r="F566">
+        <v>0</v>
+      </c>
+      <c r="G566" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="567" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A567" s="1">
+        <v>46038</v>
+      </c>
+      <c r="B567" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C567" t="s">
+        <v>98</v>
+      </c>
+      <c r="D567">
+        <v>4</v>
+      </c>
+      <c r="E567">
+        <v>20</v>
+      </c>
+      <c r="F567">
+        <v>0</v>
+      </c>
+      <c r="G567" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="568" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A568" s="1">
+        <v>46038</v>
+      </c>
+      <c r="B568" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C568" t="s">
+        <v>98</v>
+      </c>
+      <c r="D568">
+        <v>3</v>
+      </c>
+      <c r="E568">
+        <v>6</v>
+      </c>
+      <c r="F568">
+        <v>0</v>
+      </c>
+      <c r="G568" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="569" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A569" s="1">
+        <v>46038</v>
+      </c>
+      <c r="B569" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C569" t="s">
+        <v>103</v>
+      </c>
+      <c r="D569">
+        <v>1</v>
+      </c>
+      <c r="E569">
+        <v>15</v>
+      </c>
+      <c r="F569">
+        <v>15</v>
+      </c>
+      <c r="G569" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="570" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A570" s="1">
+        <v>46038</v>
+      </c>
+      <c r="B570" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C570" t="s">
+        <v>103</v>
+      </c>
+      <c r="D570">
+        <v>1</v>
+      </c>
+      <c r="E570">
+        <v>15</v>
+      </c>
+      <c r="F570">
+        <v>15</v>
+      </c>
+      <c r="G570" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="571" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A571" s="1">
+        <v>46038</v>
+      </c>
+      <c r="B571" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C571" t="s">
+        <v>103</v>
+      </c>
+      <c r="D571">
+        <v>1</v>
+      </c>
+      <c r="E571">
+        <v>15</v>
+      </c>
+      <c r="F571">
+        <v>15</v>
+      </c>
+      <c r="G571" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="572" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A572" s="1">
+        <v>46038</v>
+      </c>
+      <c r="B572" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C572" t="s">
+        <v>103</v>
+      </c>
+      <c r="D572">
+        <v>2</v>
+      </c>
+      <c r="E572">
+        <v>25</v>
+      </c>
+      <c r="F572">
+        <v>20</v>
+      </c>
+      <c r="G572" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="573" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A573" s="1">
+        <v>46038</v>
+      </c>
+      <c r="B573" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C573" t="s">
+        <v>104</v>
+      </c>
+      <c r="D573">
+        <v>2</v>
+      </c>
+      <c r="E573">
+        <v>15</v>
+      </c>
+      <c r="F573">
+        <v>0</v>
+      </c>
+      <c r="G573" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -12400,7 +14750,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C015AB5-FA38-994A-89E4-279E0D11AC16}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -12452,10 +14802,10 @@
         <v>45904</v>
       </c>
       <c r="B3" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="C3" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="D3" t="s">
         <v>187</v>
@@ -12486,10 +14836,10 @@
         <v>45934</v>
       </c>
       <c r="B5" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="C5" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="D5" t="s">
         <v>187</v>
@@ -12520,10 +14870,10 @@
         <v>45965</v>
       </c>
       <c r="B7" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="C7" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="D7" t="s">
         <v>187</v>
@@ -12554,16 +14904,50 @@
         <v>45995</v>
       </c>
       <c r="B9" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="C9" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="D9" t="s">
         <v>187</v>
       </c>
       <c r="E9">
         <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>46034</v>
+      </c>
+      <c r="B10" t="s">
+        <v>207</v>
+      </c>
+      <c r="C10" t="s">
+        <v>208</v>
+      </c>
+      <c r="D10" t="s">
+        <v>187</v>
+      </c>
+      <c r="E10">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>46034</v>
+      </c>
+      <c r="B11" t="s">
+        <v>188</v>
+      </c>
+      <c r="C11" t="s">
+        <v>189</v>
+      </c>
+      <c r="D11" t="s">
+        <v>187</v>
+      </c>
+      <c r="E11">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/data_samples/workout_entry_template.xlsx
+++ b/data_samples/workout_entry_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amlim/Downloads/azure-fit-platform/data_samples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98978BD8-9387-614B-B63C-35F326FA0BB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D815A4A9-A855-DE47-93E8-342CC5197530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16100" xr2:uid="{5828482D-6AAB-A34A-A077-81D95F329610}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16140" xr2:uid="{5828482D-6AAB-A34A-A077-81D95F329610}"/>
   </bookViews>
   <sheets>
     <sheet name="workout_entry_template" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1962" uniqueCount="217">
   <si>
     <t>date</t>
   </si>
@@ -658,6 +658,21 @@
   </si>
   <si>
     <t>Band-Assisted Tuck Planche</t>
+  </si>
+  <si>
+    <t>Calf Press</t>
+  </si>
+  <si>
+    <t>Curtsy Lunges</t>
+  </si>
+  <si>
+    <t>Lower Back Extensions</t>
+  </si>
+  <si>
+    <t>Standing Calf Raises</t>
+  </si>
+  <si>
+    <t>Baseball Swings</t>
   </si>
 </sst>
 </file>
@@ -1528,7 +1543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09805D65-2793-1C46-AB3E-4E9435A12762}">
-  <dimension ref="A1:H573"/>
+  <dimension ref="A1:H635"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.6640625" customWidth="1"/>
@@ -14729,6 +14744,1432 @@
       </c>
       <c r="G573" t="s">
         <v>125</v>
+      </c>
+    </row>
+    <row r="574" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A574" s="1">
+        <v>46041</v>
+      </c>
+      <c r="B574" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C574" t="s">
+        <v>105</v>
+      </c>
+      <c r="D574">
+        <v>1</v>
+      </c>
+      <c r="E574">
+        <v>10</v>
+      </c>
+      <c r="F574">
+        <v>0</v>
+      </c>
+      <c r="G574" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="575" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A575" s="1">
+        <v>46041</v>
+      </c>
+      <c r="B575" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C575" t="s">
+        <v>105</v>
+      </c>
+      <c r="D575">
+        <v>1</v>
+      </c>
+      <c r="E575">
+        <v>12</v>
+      </c>
+      <c r="F575">
+        <v>0</v>
+      </c>
+      <c r="G575" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="576" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A576" s="1">
+        <v>46041</v>
+      </c>
+      <c r="B576" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C576" t="s">
+        <v>105</v>
+      </c>
+      <c r="D576">
+        <v>1</v>
+      </c>
+      <c r="E576">
+        <v>12</v>
+      </c>
+      <c r="F576">
+        <v>0</v>
+      </c>
+      <c r="G576" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="577" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A577" s="1">
+        <v>46041</v>
+      </c>
+      <c r="B577" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C577" t="s">
+        <v>105</v>
+      </c>
+      <c r="D577">
+        <v>1</v>
+      </c>
+      <c r="E577">
+        <v>12</v>
+      </c>
+      <c r="F577">
+        <v>0</v>
+      </c>
+      <c r="G577" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="578" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A578" s="1">
+        <v>46041</v>
+      </c>
+      <c r="B578" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C578" t="s">
+        <v>103</v>
+      </c>
+      <c r="D578">
+        <v>3</v>
+      </c>
+      <c r="E578">
+        <v>8</v>
+      </c>
+      <c r="F578">
+        <v>264</v>
+      </c>
+      <c r="G578" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="579" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A579" s="1">
+        <v>46041</v>
+      </c>
+      <c r="B579" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C579" t="s">
+        <v>103</v>
+      </c>
+      <c r="D579">
+        <v>2</v>
+      </c>
+      <c r="E579">
+        <v>10</v>
+      </c>
+      <c r="F579">
+        <v>120</v>
+      </c>
+      <c r="G579" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="580" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A580" s="1">
+        <v>46041</v>
+      </c>
+      <c r="B580" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C580" t="s">
+        <v>103</v>
+      </c>
+      <c r="D580">
+        <v>2</v>
+      </c>
+      <c r="E580">
+        <v>8</v>
+      </c>
+      <c r="F580">
+        <v>140</v>
+      </c>
+      <c r="G580" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="581" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A581" s="1">
+        <v>46041</v>
+      </c>
+      <c r="B581" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C581" t="s">
+        <v>103</v>
+      </c>
+      <c r="D581">
+        <v>3</v>
+      </c>
+      <c r="E581">
+        <v>10</v>
+      </c>
+      <c r="F581">
+        <v>120</v>
+      </c>
+      <c r="G581" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="582" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A582" s="1">
+        <v>46041</v>
+      </c>
+      <c r="B582" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C582" t="s">
+        <v>103</v>
+      </c>
+      <c r="D582">
+        <v>4</v>
+      </c>
+      <c r="E582">
+        <v>12</v>
+      </c>
+      <c r="F582">
+        <v>205</v>
+      </c>
+      <c r="G582" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="583" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A583" s="1">
+        <v>46041</v>
+      </c>
+      <c r="B583" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C583" t="s">
+        <v>103</v>
+      </c>
+      <c r="D583">
+        <v>2</v>
+      </c>
+      <c r="E583">
+        <v>10</v>
+      </c>
+      <c r="F583">
+        <v>100</v>
+      </c>
+      <c r="G583" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="584" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A584" s="1">
+        <v>46041</v>
+      </c>
+      <c r="B584" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C584" t="s">
+        <v>103</v>
+      </c>
+      <c r="D584">
+        <v>2</v>
+      </c>
+      <c r="E584">
+        <v>6</v>
+      </c>
+      <c r="F584">
+        <v>110</v>
+      </c>
+      <c r="G584" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="585" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A585" s="1">
+        <v>46041</v>
+      </c>
+      <c r="B585" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C585" t="s">
+        <v>103</v>
+      </c>
+      <c r="D585">
+        <v>4</v>
+      </c>
+      <c r="E585">
+        <v>12</v>
+      </c>
+      <c r="F585">
+        <v>130</v>
+      </c>
+      <c r="G585" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="586" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A586" s="1">
+        <v>46042</v>
+      </c>
+      <c r="B586" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C586" t="s">
+        <v>105</v>
+      </c>
+      <c r="D586">
+        <v>2</v>
+      </c>
+      <c r="E586">
+        <v>15</v>
+      </c>
+      <c r="F586">
+        <v>0</v>
+      </c>
+      <c r="G586" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="587" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A587" s="1">
+        <v>46042</v>
+      </c>
+      <c r="B587" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C587" t="s">
+        <v>105</v>
+      </c>
+      <c r="D587">
+        <v>2</v>
+      </c>
+      <c r="E587">
+        <v>15</v>
+      </c>
+      <c r="F587">
+        <v>0</v>
+      </c>
+      <c r="G587" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="588" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A588" s="1">
+        <v>46042</v>
+      </c>
+      <c r="B588" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C588" t="s">
+        <v>104</v>
+      </c>
+      <c r="D588">
+        <v>3</v>
+      </c>
+      <c r="E588">
+        <v>15</v>
+      </c>
+      <c r="F588">
+        <v>0</v>
+      </c>
+      <c r="G588" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="589" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A589" s="1">
+        <v>46042</v>
+      </c>
+      <c r="B589" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C589" t="s">
+        <v>103</v>
+      </c>
+      <c r="D589">
+        <v>3</v>
+      </c>
+      <c r="E589">
+        <v>15</v>
+      </c>
+      <c r="F589">
+        <v>0</v>
+      </c>
+      <c r="G589" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="590" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A590" s="1">
+        <v>46042</v>
+      </c>
+      <c r="B590" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C590" t="s">
+        <v>98</v>
+      </c>
+      <c r="D590">
+        <v>4</v>
+      </c>
+      <c r="E590">
+        <v>30</v>
+      </c>
+      <c r="F590">
+        <v>0</v>
+      </c>
+      <c r="G590" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="591" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A591" s="1">
+        <v>46042</v>
+      </c>
+      <c r="B591" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C591" t="s">
+        <v>98</v>
+      </c>
+      <c r="D591">
+        <v>3</v>
+      </c>
+      <c r="E591">
+        <v>6</v>
+      </c>
+      <c r="F591">
+        <v>0</v>
+      </c>
+      <c r="G591" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="592" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A592" s="1">
+        <v>46042</v>
+      </c>
+      <c r="B592" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C592" t="s">
+        <v>103</v>
+      </c>
+      <c r="D592">
+        <v>2</v>
+      </c>
+      <c r="E592">
+        <v>8</v>
+      </c>
+      <c r="F592">
+        <v>25</v>
+      </c>
+      <c r="G592" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="593" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A593" s="1">
+        <v>46042</v>
+      </c>
+      <c r="B593" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C593" t="s">
+        <v>103</v>
+      </c>
+      <c r="D593">
+        <v>2</v>
+      </c>
+      <c r="E593">
+        <v>6</v>
+      </c>
+      <c r="F593">
+        <v>30</v>
+      </c>
+      <c r="G593" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="594" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A594" s="1">
+        <v>46042</v>
+      </c>
+      <c r="B594" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C594" t="s">
+        <v>103</v>
+      </c>
+      <c r="D594">
+        <v>3</v>
+      </c>
+      <c r="E594">
+        <v>15</v>
+      </c>
+      <c r="F594">
+        <v>0</v>
+      </c>
+      <c r="G594" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="595" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A595" s="1">
+        <v>46042</v>
+      </c>
+      <c r="B595" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C595" t="s">
+        <v>98</v>
+      </c>
+      <c r="D595">
+        <v>4</v>
+      </c>
+      <c r="E595">
+        <v>8</v>
+      </c>
+      <c r="F595">
+        <v>0</v>
+      </c>
+      <c r="G595" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="596" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A596" s="1">
+        <v>46043</v>
+      </c>
+      <c r="B596" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C596" t="s">
+        <v>105</v>
+      </c>
+      <c r="D596">
+        <v>1</v>
+      </c>
+      <c r="E596">
+        <v>12</v>
+      </c>
+      <c r="F596">
+        <v>0</v>
+      </c>
+      <c r="G596" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="597" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A597" s="1">
+        <v>46043</v>
+      </c>
+      <c r="B597" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C597" t="s">
+        <v>105</v>
+      </c>
+      <c r="D597">
+        <v>1</v>
+      </c>
+      <c r="E597">
+        <v>12</v>
+      </c>
+      <c r="F597">
+        <v>0</v>
+      </c>
+      <c r="G597" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="598" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A598" s="1">
+        <v>46043</v>
+      </c>
+      <c r="B598" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C598" t="s">
+        <v>105</v>
+      </c>
+      <c r="D598">
+        <v>1</v>
+      </c>
+      <c r="E598">
+        <v>12</v>
+      </c>
+      <c r="F598">
+        <v>0</v>
+      </c>
+      <c r="G598" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="599" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A599" s="1">
+        <v>46043</v>
+      </c>
+      <c r="B599" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C599" t="s">
+        <v>103</v>
+      </c>
+      <c r="D599">
+        <v>4</v>
+      </c>
+      <c r="E599">
+        <v>10</v>
+      </c>
+      <c r="F599">
+        <v>20</v>
+      </c>
+      <c r="G599" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="600" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A600" s="1">
+        <v>46043</v>
+      </c>
+      <c r="B600" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C600" t="s">
+        <v>103</v>
+      </c>
+      <c r="D600">
+        <v>5</v>
+      </c>
+      <c r="E600">
+        <v>6</v>
+      </c>
+      <c r="F600">
+        <v>40</v>
+      </c>
+      <c r="G600" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="601" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A601" s="1">
+        <v>46043</v>
+      </c>
+      <c r="B601" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C601" t="s">
+        <v>103</v>
+      </c>
+      <c r="D601">
+        <v>3</v>
+      </c>
+      <c r="E601">
+        <v>15</v>
+      </c>
+      <c r="F601">
+        <v>0</v>
+      </c>
+      <c r="G601" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="602" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A602" s="1">
+        <v>46043</v>
+      </c>
+      <c r="B602" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C602" t="s">
+        <v>103</v>
+      </c>
+      <c r="D602">
+        <v>4</v>
+      </c>
+      <c r="E602">
+        <v>5</v>
+      </c>
+      <c r="F602">
+        <v>0</v>
+      </c>
+      <c r="G602" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="603" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A603" s="1">
+        <v>46043</v>
+      </c>
+      <c r="B603" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C603" t="s">
+        <v>103</v>
+      </c>
+      <c r="D603">
+        <v>3</v>
+      </c>
+      <c r="E603">
+        <v>10</v>
+      </c>
+      <c r="F603">
+        <v>0</v>
+      </c>
+      <c r="G603" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="604" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A604" s="1">
+        <v>46045</v>
+      </c>
+      <c r="B604" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C604" t="s">
+        <v>105</v>
+      </c>
+      <c r="D604">
+        <v>2</v>
+      </c>
+      <c r="E604">
+        <v>15</v>
+      </c>
+      <c r="F604">
+        <v>0</v>
+      </c>
+      <c r="G604" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="605" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A605" s="1">
+        <v>46045</v>
+      </c>
+      <c r="B605" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C605" t="s">
+        <v>105</v>
+      </c>
+      <c r="D605">
+        <v>2</v>
+      </c>
+      <c r="E605">
+        <v>15</v>
+      </c>
+      <c r="F605">
+        <v>0</v>
+      </c>
+      <c r="G605" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="606" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A606" s="1">
+        <v>46045</v>
+      </c>
+      <c r="B606" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C606" t="s">
+        <v>105</v>
+      </c>
+      <c r="D606">
+        <v>1</v>
+      </c>
+      <c r="E606">
+        <v>10</v>
+      </c>
+      <c r="F606">
+        <v>0</v>
+      </c>
+      <c r="G606" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="607" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A607" s="1">
+        <v>46045</v>
+      </c>
+      <c r="B607" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C607" t="s">
+        <v>105</v>
+      </c>
+      <c r="D607">
+        <v>1</v>
+      </c>
+      <c r="E607">
+        <v>15</v>
+      </c>
+      <c r="F607">
+        <v>5</v>
+      </c>
+      <c r="G607" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="608" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A608" s="1">
+        <v>46045</v>
+      </c>
+      <c r="B608" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C608" t="s">
+        <v>104</v>
+      </c>
+      <c r="D608">
+        <v>4</v>
+      </c>
+      <c r="E608">
+        <v>16</v>
+      </c>
+      <c r="F608">
+        <v>0</v>
+      </c>
+      <c r="G608" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="609" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A609" s="1">
+        <v>46045</v>
+      </c>
+      <c r="B609" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C609" t="s">
+        <v>103</v>
+      </c>
+      <c r="D609">
+        <v>1</v>
+      </c>
+      <c r="E609">
+        <v>15</v>
+      </c>
+      <c r="F609">
+        <v>15</v>
+      </c>
+      <c r="G609" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="610" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A610" s="1">
+        <v>46045</v>
+      </c>
+      <c r="B610" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C610" t="s">
+        <v>103</v>
+      </c>
+      <c r="D610">
+        <v>1</v>
+      </c>
+      <c r="E610">
+        <v>15</v>
+      </c>
+      <c r="F610">
+        <v>15</v>
+      </c>
+      <c r="G610" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="611" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A611" s="1">
+        <v>46045</v>
+      </c>
+      <c r="B611" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C611" t="s">
+        <v>103</v>
+      </c>
+      <c r="D611">
+        <v>1</v>
+      </c>
+      <c r="E611">
+        <v>15</v>
+      </c>
+      <c r="F611">
+        <v>15</v>
+      </c>
+      <c r="G611" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="612" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A612" s="1">
+        <v>46045</v>
+      </c>
+      <c r="B612" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C612" t="s">
+        <v>104</v>
+      </c>
+      <c r="D612">
+        <v>4</v>
+      </c>
+      <c r="E612">
+        <v>10</v>
+      </c>
+      <c r="F612">
+        <v>0</v>
+      </c>
+      <c r="G612" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="613" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A613" s="1">
+        <v>46045</v>
+      </c>
+      <c r="B613" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C613" t="s">
+        <v>98</v>
+      </c>
+      <c r="D613">
+        <v>3</v>
+      </c>
+      <c r="E613">
+        <v>25</v>
+      </c>
+      <c r="F613">
+        <v>0</v>
+      </c>
+      <c r="G613" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="614" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A614" s="1">
+        <v>46045</v>
+      </c>
+      <c r="B614" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C614" t="s">
+        <v>103</v>
+      </c>
+      <c r="D614">
+        <v>4</v>
+      </c>
+      <c r="E614">
+        <v>8</v>
+      </c>
+      <c r="F614">
+        <v>70</v>
+      </c>
+      <c r="G614" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="615" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A615" s="1">
+        <v>46045</v>
+      </c>
+      <c r="B615" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C615" t="s">
+        <v>103</v>
+      </c>
+      <c r="D615">
+        <v>4</v>
+      </c>
+      <c r="E615">
+        <v>10</v>
+      </c>
+      <c r="F615">
+        <v>0</v>
+      </c>
+      <c r="G615" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="616" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A616" s="1">
+        <v>46045</v>
+      </c>
+      <c r="B616" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C616" t="s">
+        <v>103</v>
+      </c>
+      <c r="D616">
+        <v>3</v>
+      </c>
+      <c r="E616">
+        <v>6</v>
+      </c>
+      <c r="F616">
+        <v>30</v>
+      </c>
+      <c r="G616" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="617" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A617" s="1">
+        <v>46046</v>
+      </c>
+      <c r="B617" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C617" t="s">
+        <v>105</v>
+      </c>
+      <c r="D617">
+        <v>1</v>
+      </c>
+      <c r="E617">
+        <v>10</v>
+      </c>
+      <c r="F617">
+        <v>0</v>
+      </c>
+      <c r="G617" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="618" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A618" s="1">
+        <v>46046</v>
+      </c>
+      <c r="B618" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C618" t="s">
+        <v>105</v>
+      </c>
+      <c r="D618">
+        <v>1</v>
+      </c>
+      <c r="E618">
+        <v>10</v>
+      </c>
+      <c r="F618">
+        <v>0</v>
+      </c>
+      <c r="G618" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="619" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A619" s="1">
+        <v>46046</v>
+      </c>
+      <c r="B619" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C619" t="s">
+        <v>103</v>
+      </c>
+      <c r="D619">
+        <v>4</v>
+      </c>
+      <c r="E619">
+        <v>8</v>
+      </c>
+      <c r="F619">
+        <v>110</v>
+      </c>
+      <c r="G619" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="620" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A620" s="1">
+        <v>46046</v>
+      </c>
+      <c r="B620" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C620" t="s">
+        <v>103</v>
+      </c>
+      <c r="D620">
+        <v>4</v>
+      </c>
+      <c r="E620">
+        <v>10</v>
+      </c>
+      <c r="F620">
+        <v>115</v>
+      </c>
+      <c r="G620" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="621" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A621" s="1">
+        <v>46046</v>
+      </c>
+      <c r="B621" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C621" t="s">
+        <v>103</v>
+      </c>
+      <c r="D621">
+        <v>3</v>
+      </c>
+      <c r="E621">
+        <v>10</v>
+      </c>
+      <c r="F621">
+        <v>25</v>
+      </c>
+      <c r="G621" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="622" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A622" s="1">
+        <v>46046</v>
+      </c>
+      <c r="B622" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C622" t="s">
+        <v>103</v>
+      </c>
+      <c r="D622">
+        <v>2</v>
+      </c>
+      <c r="E622">
+        <v>10</v>
+      </c>
+      <c r="F622">
+        <v>230</v>
+      </c>
+      <c r="G622" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="623" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A623" s="1">
+        <v>46046</v>
+      </c>
+      <c r="B623" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C623" t="s">
+        <v>103</v>
+      </c>
+      <c r="D623">
+        <v>2</v>
+      </c>
+      <c r="E623">
+        <v>8</v>
+      </c>
+      <c r="F623">
+        <v>270</v>
+      </c>
+      <c r="G623" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="624" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A624" s="1">
+        <v>46046</v>
+      </c>
+      <c r="B624" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C624" t="s">
+        <v>103</v>
+      </c>
+      <c r="D624">
+        <v>2</v>
+      </c>
+      <c r="E624">
+        <v>10</v>
+      </c>
+      <c r="F624">
+        <v>15</v>
+      </c>
+      <c r="G624" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="625" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A625" s="1">
+        <v>46046</v>
+      </c>
+      <c r="B625" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C625" t="s">
+        <v>103</v>
+      </c>
+      <c r="D625">
+        <v>2</v>
+      </c>
+      <c r="E625">
+        <v>10</v>
+      </c>
+      <c r="F625">
+        <v>25</v>
+      </c>
+      <c r="G625" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="626" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A626" s="1">
+        <v>46049</v>
+      </c>
+      <c r="B626" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C626" t="s">
+        <v>98</v>
+      </c>
+      <c r="D626">
+        <v>4</v>
+      </c>
+      <c r="E626">
+        <v>15</v>
+      </c>
+      <c r="F626">
+        <v>0</v>
+      </c>
+      <c r="G626" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="627" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A627" s="1">
+        <v>46049</v>
+      </c>
+      <c r="B627" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C627" t="s">
+        <v>104</v>
+      </c>
+      <c r="D627">
+        <v>4</v>
+      </c>
+      <c r="E627">
+        <v>15</v>
+      </c>
+      <c r="F627">
+        <v>0</v>
+      </c>
+      <c r="G627" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="628" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A628" s="1">
+        <v>46049</v>
+      </c>
+      <c r="B628" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C628" t="s">
+        <v>104</v>
+      </c>
+      <c r="D628">
+        <v>4</v>
+      </c>
+      <c r="E628">
+        <v>15</v>
+      </c>
+      <c r="F628">
+        <v>0</v>
+      </c>
+      <c r="G628" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="629" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A629" s="1">
+        <v>46049</v>
+      </c>
+      <c r="B629" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C629" t="s">
+        <v>104</v>
+      </c>
+      <c r="D629">
+        <v>3</v>
+      </c>
+      <c r="E629">
+        <v>25</v>
+      </c>
+      <c r="F629">
+        <v>0</v>
+      </c>
+      <c r="G629" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="630" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A630" s="1">
+        <v>46049</v>
+      </c>
+      <c r="B630" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C630" t="s">
+        <v>98</v>
+      </c>
+      <c r="D630">
+        <v>4</v>
+      </c>
+      <c r="E630">
+        <v>10</v>
+      </c>
+      <c r="F630">
+        <v>0</v>
+      </c>
+      <c r="G630" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="631" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A631" s="1">
+        <v>46049</v>
+      </c>
+      <c r="B631" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C631" t="s">
+        <v>103</v>
+      </c>
+      <c r="D631">
+        <v>5</v>
+      </c>
+      <c r="E631">
+        <v>5</v>
+      </c>
+      <c r="F631">
+        <v>30</v>
+      </c>
+      <c r="G631" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="632" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A632" s="1">
+        <v>46049</v>
+      </c>
+      <c r="B632" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C632" t="s">
+        <v>103</v>
+      </c>
+      <c r="D632">
+        <v>3</v>
+      </c>
+      <c r="E632">
+        <v>5</v>
+      </c>
+      <c r="F632">
+        <v>0</v>
+      </c>
+      <c r="G632" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="633" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A633" s="1">
+        <v>46049</v>
+      </c>
+      <c r="B633" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C633" t="s">
+        <v>105</v>
+      </c>
+      <c r="D633">
+        <v>2</v>
+      </c>
+      <c r="E633">
+        <v>15</v>
+      </c>
+      <c r="F633">
+        <v>0</v>
+      </c>
+      <c r="G633" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="634" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A634" s="1">
+        <v>46049</v>
+      </c>
+      <c r="B634" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C634" t="s">
+        <v>105</v>
+      </c>
+      <c r="D634">
+        <v>2</v>
+      </c>
+      <c r="E634">
+        <v>15</v>
+      </c>
+      <c r="F634">
+        <v>0</v>
+      </c>
+      <c r="G634" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="635" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A635" s="1">
+        <v>46049</v>
+      </c>
+      <c r="B635" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C635" t="s">
+        <v>105</v>
+      </c>
+      <c r="D635">
+        <v>1</v>
+      </c>
+      <c r="E635">
+        <v>10</v>
+      </c>
+      <c r="F635">
+        <v>0</v>
+      </c>
+      <c r="G635" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -14750,7 +16191,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C015AB5-FA38-994A-89E4-279E0D11AC16}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -14948,6 +16389,40 @@
       </c>
       <c r="E11">
         <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>46049</v>
+      </c>
+      <c r="B12" t="s">
+        <v>188</v>
+      </c>
+      <c r="C12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D12" t="s">
+        <v>187</v>
+      </c>
+      <c r="E12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>46049</v>
+      </c>
+      <c r="B13" t="s">
+        <v>207</v>
+      </c>
+      <c r="C13" t="s">
+        <v>208</v>
+      </c>
+      <c r="D13" t="s">
+        <v>187</v>
+      </c>
+      <c r="E13">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
